--- a/课堂在线/importTopicTemplate.xlsx
+++ b/课堂在线/importTopicTemplate.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\srr17\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\2025\教材\智慧水利平台架构与开发\课堂在线\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{49B98AF0-776D-43A2-BF8C-259DA4608F2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A71EAB2-1B80-4918-8FAD-93C5FEB358EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet3" sheetId="3" r:id="rId1"/>
+    <sheet name="Sheet4" sheetId="6" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="870" uniqueCount="291">
   <si>
     <t>一级知识点</t>
   </si>
@@ -78,40 +79,7 @@
     <t>知识点说明</t>
   </si>
   <si>
-    <t>标签名1</t>
-  </si>
-  <si>
-    <t>标签名1.1</t>
-  </si>
-  <si>
-    <t>标签名1.1.1</t>
-  </si>
-  <si>
-    <t>标签名1.1.2</t>
-  </si>
-  <si>
-    <t>标签名1.1.3;标签名1.2.1</t>
-  </si>
-  <si>
-    <t>标签名2</t>
-  </si>
-  <si>
-    <t>考点;难点</t>
-  </si>
-  <si>
     <t>记忆</t>
-  </si>
-  <si>
-    <t>事实性</t>
-  </si>
-  <si>
-    <t>标签名1.1.3</t>
-  </si>
-  <si>
-    <t>标签名1.2</t>
-  </si>
-  <si>
-    <t>标签名1.2.1</t>
   </si>
   <si>
     <t xml:space="preserve">使用说明：
@@ -126,12 +94,1081 @@
 </t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
+  <si>
+    <t>理解</t>
+  </si>
+  <si>
+    <t>概念性</t>
+  </si>
+  <si>
+    <t>难点</t>
+  </si>
+  <si>
+    <t>分析</t>
+  </si>
+  <si>
+    <t>重点</t>
+  </si>
+  <si>
+    <t>应用</t>
+  </si>
+  <si>
+    <t>程序性</t>
+  </si>
+  <si>
+    <t>考点</t>
+  </si>
+  <si>
+    <t>评价</t>
+  </si>
+  <si>
+    <t>功能需求</t>
+  </si>
+  <si>
+    <t>元认知</t>
+  </si>
+  <si>
+    <t>实践</t>
+  </si>
+  <si>
+    <t>事实性</t>
+  </si>
+  <si>
+    <t>原型</t>
+  </si>
+  <si>
+    <t>性能</t>
+  </si>
+  <si>
+    <t>需求分析（第2章）</t>
+  </si>
+  <si>
+    <t>软件开发项目管理（第4章）</t>
+  </si>
+  <si>
+    <t>项目特征</t>
+  </si>
+  <si>
+    <t>用原型澄清需求</t>
+  </si>
+  <si>
+    <t>访谈</t>
+  </si>
+  <si>
+    <r>
+      <t>说明：本稿按你系统的</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>空白对齐</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>规范输出，允许使用到</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>七级</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>且不跳级；属性列（前置/后置/关联/标签/认知维度/分类/教学目标/知识点说明）</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>已填写</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（从三级起为主）。关系遵循“任意两知识点之间仅一种关系；新导入覆盖旧关系”，多个条目用英文分号</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>分隔。</t>
+    </r>
+  </si>
+  <si>
+    <t>第2章：需求分析（细化，属性已填）</t>
+  </si>
+  <si>
+    <t>理解需求分析定位</t>
+  </si>
+  <si>
+    <t>连接业务目标与技术实现，产出SRS与范围基线</t>
+  </si>
+  <si>
+    <t>2.1 需求工程概述</t>
+  </si>
+  <si>
+    <t>2.2 利益相关者与业务域</t>
+  </si>
+  <si>
+    <t>2.3 需求获取与分析</t>
+  </si>
+  <si>
+    <t>认识需求工程活动</t>
+  </si>
+  <si>
+    <t>获取-分析-规格化-验证-管理的闭环</t>
+  </si>
+  <si>
+    <t>活动与产物</t>
+  </si>
+  <si>
+    <t>2.4 需求规格说明</t>
+  </si>
+  <si>
+    <t>2.8 变更与基线</t>
+  </si>
+  <si>
+    <t>说出活动-产物映射</t>
+  </si>
+  <si>
+    <t>活动→产物：获取→原始需求；分析→模型；规格→SRS；验证→评审记录</t>
+  </si>
+  <si>
+    <t>2.10 典型需求清单</t>
+  </si>
+  <si>
+    <t>明确干系人与场景</t>
+  </si>
+  <si>
+    <t>列出角色、职责、痛点与价值主张</t>
+  </si>
+  <si>
+    <t>干系人识别</t>
+  </si>
+  <si>
+    <t>会绘制干系人地图</t>
+  </si>
+  <si>
+    <t>管理员;调度员;巡检员;水文技师;公众;第三方机构等</t>
+  </si>
+  <si>
+    <t>业务域界定</t>
+  </si>
+  <si>
+    <t>2.5 需求建模与视图</t>
+  </si>
+  <si>
+    <t>确定边界与上下文</t>
+  </si>
+  <si>
+    <t>明确智慧水利平台覆盖的业务边界与外部系统</t>
+  </si>
+  <si>
+    <t>2.7 优先级与范围</t>
+  </si>
+  <si>
+    <t>选择合适获取方法</t>
+  </si>
+  <si>
+    <t>访谈/研讨/观察/问卷/文档分析/原型/JAD</t>
+  </si>
+  <si>
+    <t>获取方法</t>
+  </si>
+  <si>
+    <t>2.3 需求冲突处理</t>
+  </si>
+  <si>
+    <t>列举获取方法</t>
+  </si>
+  <si>
+    <t>半结构化访谈;工作坊;竞品/日志分析;现场观察</t>
+  </si>
+  <si>
+    <t>制定访谈提纲与纪要</t>
+  </si>
+  <si>
+    <t>角色、场景、痛点、期望与KPI；会后确认</t>
+  </si>
+  <si>
+    <t>低保真/高保真原型验证交互与信息架构</t>
+  </si>
+  <si>
+    <t>观察与现场走查</t>
+  </si>
+  <si>
+    <t>记录真实工作流</t>
+  </si>
+  <si>
+    <t>观察巡检/测站运维与调度流程，识别改进点</t>
+  </si>
+  <si>
+    <t>需求分析技术</t>
+  </si>
+  <si>
+    <t>掌握分析手段</t>
+  </si>
+  <si>
+    <t>亲和图/鱼骨图/5Whys/用户旅程/价值流</t>
+  </si>
+  <si>
+    <t>冲突与一致性</t>
+  </si>
+  <si>
+    <t>解决冲突并达成一致</t>
+  </si>
+  <si>
+    <t>通过权衡矩阵与决策记录化解冲突</t>
+  </si>
+  <si>
+    <t>2.4 需求规格说明（SRS）</t>
+  </si>
+  <si>
+    <t>2.6 需求质量与验证</t>
+  </si>
+  <si>
+    <t>产出规范化SRS</t>
+  </si>
+  <si>
+    <t>结构、术语、功能/非功能、约束、用例与接口</t>
+  </si>
+  <si>
+    <t>SRS 结构</t>
+  </si>
+  <si>
+    <t>列举SRS主要章节</t>
+  </si>
+  <si>
+    <t>引言;总体描述;具体需求;附录;术语与索引</t>
+  </si>
+  <si>
+    <t>术语与数据字典</t>
+  </si>
+  <si>
+    <t>明确术语口径</t>
+  </si>
+  <si>
+    <t>统一“测站;断面;库站;预警阈值;雨量;水位”等术语</t>
+  </si>
+  <si>
+    <t>需求可追踪</t>
+  </si>
+  <si>
+    <t>2.9 需求跟踪矩阵</t>
+  </si>
+  <si>
+    <t>建立RTM矩阵</t>
+  </si>
+  <si>
+    <t>需求ID↔用例↔设计↔实现↔测试用例↔验证</t>
+  </si>
+  <si>
+    <t>会选择合适建模视图</t>
+  </si>
+  <si>
+    <t>用例、上下文、DFD、领域模型、活动/状态图、BPMN</t>
+  </si>
+  <si>
+    <t>用例图</t>
+  </si>
+  <si>
+    <t>2.11 用例与用户故事</t>
+  </si>
+  <si>
+    <t>识别参与者与用例</t>
+  </si>
+  <si>
+    <t>管理员;调度员;巡检员;公众;外部系统</t>
+  </si>
+  <si>
+    <t>上下文图（系统边界）</t>
+  </si>
+  <si>
+    <t>明确系统边界与接口</t>
+  </si>
+  <si>
+    <t>与测站RTU/第三方平台/短信网关/政务网等交互</t>
+  </si>
+  <si>
+    <t>领域模型（UML类图）</t>
+  </si>
+  <si>
+    <t>提炼核心实体与关系</t>
+  </si>
+  <si>
+    <t>测站;传感器;采样;告警;工单;水库;河段</t>
+  </si>
+  <si>
+    <t>流程与活动（BPMN/活动图）</t>
+  </si>
+  <si>
+    <t>表达业务流程</t>
+  </si>
+  <si>
+    <t>巡检→上报→派单→处理→复核→归档</t>
+  </si>
+  <si>
+    <t>检查SRS质量</t>
+  </si>
+  <si>
+    <t>一致;完整;可验证;可追踪;无歧义;必要;可行</t>
+  </si>
+  <si>
+    <t>验证技术</t>
+  </si>
+  <si>
+    <t>会做需求评审</t>
+  </si>
+  <si>
+    <t>走查;评审;原型可用性测试;验收标准GWT</t>
+  </si>
+  <si>
+    <t>2.7 需求优先级与范围管理</t>
+  </si>
+  <si>
+    <t>控制范围与节奏</t>
+  </si>
+  <si>
+    <t>MoSCoW;Kano;价值-成本矩阵;发布计划</t>
+  </si>
+  <si>
+    <t>优先级方法</t>
+  </si>
+  <si>
+    <t>记忆常用方法</t>
+  </si>
+  <si>
+    <t>MoSCoW（必须;应当;可以;不会）;Kano</t>
+  </si>
+  <si>
+    <t>发布与范围基线</t>
+  </si>
+  <si>
+    <t>制定版本计划</t>
+  </si>
+  <si>
+    <t>以迭代/里程碑管理交付范围，建立基线</t>
+  </si>
+  <si>
+    <t>2.8 变更与基线管理</t>
+  </si>
+  <si>
+    <t>管理</t>
+  </si>
+  <si>
+    <t>规范变更流程</t>
+  </si>
+  <si>
+    <t>CR立项→评估→CCB决策→更新基线→通知各方</t>
+  </si>
+  <si>
+    <t>变更控制流程</t>
+  </si>
+  <si>
+    <t>记住关键环节</t>
+  </si>
+  <si>
+    <t>影响分析;成本/价值评估;回滚方案</t>
+  </si>
+  <si>
+    <t>2.9 需求跟踪矩阵（RTM）</t>
+  </si>
+  <si>
+    <t>2.4 需求可追踪</t>
+  </si>
+  <si>
+    <t>完成端到端追踪</t>
+  </si>
+  <si>
+    <t>需求-设计-实现-测试用例-缺陷-验收闭环</t>
+  </si>
+  <si>
+    <t>2.10 智慧水利典型需求清单</t>
+  </si>
+  <si>
+    <t>3.10 架构蓝图</t>
+  </si>
+  <si>
+    <t>梳理平台能力清单</t>
+  </si>
+  <si>
+    <t>功能与非功能需求分层</t>
+  </si>
+  <si>
+    <t>明确核心功能</t>
+  </si>
+  <si>
+    <t>采集;存储;展示;告警;分析;预测;决策;工单</t>
+  </si>
+  <si>
+    <t>数据采集</t>
+  </si>
+  <si>
+    <t>数据管理</t>
+  </si>
+  <si>
+    <t>采集来源与协议</t>
+  </si>
+  <si>
+    <t>雨量;水位;流量;水质；RTU;LoRa/NB-IoT/4G;MQTT/HTTP</t>
+  </si>
+  <si>
+    <t>可视化展示</t>
+  </si>
+  <si>
+    <t>数据入湖与治理</t>
+  </si>
+  <si>
+    <t>校验;清洗;时序存储;空间索引;元数据管理</t>
+  </si>
+  <si>
+    <t>可视化展示（GIS）</t>
+  </si>
+  <si>
+    <t>告警与联动</t>
+  </si>
+  <si>
+    <t>地图与图表联动</t>
+  </si>
+  <si>
+    <t>矢量/栅格底图;图层;点线面;业务专题图</t>
+  </si>
+  <si>
+    <t>模型与预测</t>
+  </si>
+  <si>
+    <t>定义阈值与事件</t>
+  </si>
+  <si>
+    <t>阈值/趋势/复合规则;短信/微信/广播联动</t>
+  </si>
+  <si>
+    <t>调度与决策</t>
+  </si>
+  <si>
+    <t>接入水文模型</t>
+  </si>
+  <si>
+    <t>降雨径流/洪水演进/库调度模型与参数校准</t>
+  </si>
+  <si>
+    <t>工单与巡检</t>
+  </si>
+  <si>
+    <t>端到端闭环</t>
+  </si>
+  <si>
+    <t>告警转工单；巡检任务;移动端上报;闭环评价</t>
+  </si>
+  <si>
+    <t>非功能需求</t>
+  </si>
+  <si>
+    <t>明确NFR目标</t>
+  </si>
+  <si>
+    <t>可用性;性能;扩展性;安全;合规;易维护</t>
+  </si>
+  <si>
+    <t>可用性</t>
+  </si>
+  <si>
+    <t>设定SLA</t>
+  </si>
+  <si>
+    <t>99.9%可用; RTO/RPO; 业务连续性</t>
+  </si>
+  <si>
+    <t>扩展性</t>
+  </si>
+  <si>
+    <t>量化性能指标</t>
+  </si>
+  <si>
+    <t>并发;吞吐;95/99分位响应;批处理窗口</t>
+  </si>
+  <si>
+    <t>安全与合规</t>
+  </si>
+  <si>
+    <t>易维护</t>
+  </si>
+  <si>
+    <t>明确安全基线</t>
+  </si>
+  <si>
+    <t>访问控制;审计;加密;脱敏；合规与等保要求</t>
+  </si>
+  <si>
+    <t>2.5 用例图</t>
+  </si>
+  <si>
+    <t>产出可验收的故事</t>
+  </si>
+  <si>
+    <t>角色-目标-价值；INVEST；GWT验收标准</t>
+  </si>
+  <si>
+    <t>用户故事模板</t>
+  </si>
+  <si>
+    <t>记忆模板</t>
+  </si>
+  <si>
+    <t>作为&lt;角色&gt;希望&lt;目标&gt;以便&lt;价值&gt;</t>
+  </si>
+  <si>
+    <t>验收标准（GWT）</t>
+  </si>
+  <si>
+    <t>编写可验证条件</t>
+  </si>
+  <si>
+    <t>Given-When-Then 行为驱动示例</t>
+  </si>
+  <si>
+    <t>2.12 需求风险与假设约束</t>
+  </si>
+  <si>
+    <t>2.7 优先级与范围管理</t>
+  </si>
+  <si>
+    <t>识别与记录RAID</t>
+  </si>
+  <si>
+    <t>风险/假设/问题/依赖清单与应对策略</t>
+  </si>
+  <si>
+    <t>第3章：架构设计（细化，属性已填）</t>
+  </si>
+  <si>
+    <t>规范说明：</t>
+  </si>
+  <si>
+    <r>
+      <t>严格遵守你们系统的</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>空白对齐</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>：每行只在对应层级列（一级~七级）填写一个知识点，其余层级列留空。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>不跳级</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>逐层展开，可用到</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>五/六/七级</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>属性列（前置/后置/关联/标签/认知维度/分类/教学目标/知识点说明）</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>均已填写</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>；多个值用英文分号</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>分隔。</t>
+    </r>
+  </si>
+  <si>
+    <t>关系遵循“任意两知识点只存在一种关系；新导入覆盖旧关系”。</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">本文含两部分：① </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>第4章 软件开发项目管理</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">（来自课件）；② </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>第5章 前端开发技术—前端概述补充</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（补全你指出缺漏的小节）。</t>
+    </r>
+  </si>
+  <si>
+    <t>第4章：软件开发项目管理（细化，属性已填）</t>
+  </si>
+  <si>
+    <t>需求分析（第2章）;架构设计（第3章）</t>
+  </si>
+  <si>
+    <t>1.1 概述</t>
+  </si>
+  <si>
+    <t>1.5 项目活动;4.4 项目计划</t>
+  </si>
+  <si>
+    <t>认识章节目标与范围</t>
+  </si>
+  <si>
+    <t>以成本、进度、质量、风险为核心，贯穿人-过程-工具治理</t>
+  </si>
+  <si>
+    <t>1.1 软件项目管理概述</t>
+  </si>
+  <si>
+    <t>1.5 项目活动</t>
+  </si>
+  <si>
+    <t>1.4 关注点</t>
+  </si>
+  <si>
+    <t>说清管理对象</t>
+  </si>
+  <si>
+    <t>对成本;人员;进度;质量;风险进行计划与控制，使项目按既定目标完成</t>
+  </si>
+  <si>
+    <t>1.2 4P</t>
+  </si>
+  <si>
+    <t>列举特征</t>
+  </si>
+  <si>
+    <t>软件不可见性;不确定性高;过程多变;人员流动性大</t>
+  </si>
+  <si>
+    <t>关键问题</t>
+  </si>
+  <si>
+    <t>降低复杂性与控制变化</t>
+  </si>
+  <si>
+    <t>1.3 项目与过程关系</t>
+  </si>
+  <si>
+    <t>提炼关键矛盾</t>
+  </si>
+  <si>
+    <t>通过分解、基线与变更控制降低复杂度并管控变化</t>
+  </si>
+  <si>
+    <t>1.2 管理的“4P”</t>
+  </si>
+  <si>
+    <t>2. 人员组织与管理</t>
+  </si>
+  <si>
+    <t>解释4P内涵</t>
+  </si>
+  <si>
+    <t>People; Product; Process; Project 四要素构成管理基座</t>
+  </si>
+  <si>
+    <t>1.3 项目管理与过程管理的关系</t>
+  </si>
+  <si>
+    <t>4.4 项目计划</t>
+  </si>
+  <si>
+    <t>区分两类管理</t>
+  </si>
+  <si>
+    <t>项目管理面向一次性目标;过程管理提升复用性与可预期性</t>
+  </si>
+  <si>
+    <t>明确关注领域</t>
+  </si>
+  <si>
+    <t>范围;成本;进度;质量;风险;沟通;干系人;资源</t>
+  </si>
+  <si>
+    <t>5. 风险管理;6. 配置管理</t>
+  </si>
+  <si>
+    <t>掌握项目四阶段</t>
+  </si>
+  <si>
+    <t>启动;规划;实施;收尾及对应核心产物与检查点</t>
+  </si>
+  <si>
+    <t>启动阶段</t>
+  </si>
+  <si>
+    <t>完成立项与范围定义</t>
+  </si>
+  <si>
+    <t>组建团队;明确目标/范围;搭建环境</t>
+  </si>
+  <si>
+    <t>规划阶段</t>
+  </si>
+  <si>
+    <t>实施阶段</t>
+  </si>
+  <si>
+    <t>4.4 项目计划;4.5 WBS</t>
+  </si>
+  <si>
+    <t>编制计划</t>
+  </si>
+  <si>
+    <t>活动分解;成本估算;进度排程;质量/沟通/配置等配套计划</t>
+  </si>
+  <si>
+    <t>收尾阶段</t>
+  </si>
+  <si>
+    <t>3. 项目沟通管理;5. 风险管理</t>
+  </si>
+  <si>
+    <t>组织执行与监控</t>
+  </si>
+  <si>
+    <t>跟踪进度;风险控制;变更管理;阶段评审</t>
+  </si>
+  <si>
+    <t>完成验收与总结</t>
+  </si>
+  <si>
+    <t>客户验收;安装与培训;复盘与经验沉淀</t>
+  </si>
+  <si>
+    <t>二、人员组织与管理</t>
+  </si>
+  <si>
+    <t>3. 项目沟通管理</t>
+  </si>
+  <si>
+    <t>认识“人”的决定性作用</t>
+  </si>
+  <si>
+    <t>人员选择/分配/组织直接影响效率、质量与进度</t>
+  </si>
+  <si>
+    <t>人员重要性</t>
+  </si>
+  <si>
+    <t>人员组织与管理</t>
+  </si>
+  <si>
+    <t>组织结构</t>
+  </si>
+  <si>
+    <t>团队</t>
+  </si>
+  <si>
+    <t>强调以人为本</t>
+  </si>
+  <si>
+    <t>开发依赖认知与沟通;PM工作主要面向人</t>
+  </si>
+  <si>
+    <t>人员选择</t>
+  </si>
+  <si>
+    <t>组建合适团队</t>
+  </si>
+  <si>
+    <t>匹配技能谱与经验;兼顾潜力与多样性</t>
+  </si>
+  <si>
+    <t>团队（Teams）</t>
+  </si>
+  <si>
+    <t>项目沟通管理</t>
+  </si>
+  <si>
+    <t>认识团队特征</t>
+  </si>
+  <si>
+    <t>共同参与;共担责任;目标一致;开放会议;以工作产品评价</t>
+  </si>
+  <si>
+    <t>案例</t>
+  </si>
+  <si>
+    <t>比较三种组织</t>
+  </si>
+  <si>
+    <t>民主式;主程序员式;技术管理式 的适用场景与利弊</t>
+  </si>
+  <si>
+    <t>民主式</t>
+  </si>
+  <si>
+    <t>主程序员式</t>
+  </si>
+  <si>
+    <t>说明优缺点</t>
+  </si>
+  <si>
+    <t>创造力强;适合小团队;缺乏权威不利于大规模</t>
+  </si>
+  <si>
+    <t>技术管理式</t>
+  </si>
+  <si>
+    <t>沟通简单;但难觅兼具管理与技术的核心人才</t>
+  </si>
+  <si>
+    <t>技术与管理分离;需明确权限边界与协作机制</t>
+  </si>
+  <si>
+    <t>三、项目沟通管理</t>
+  </si>
+  <si>
+    <t>3.2 沟通复杂性</t>
+  </si>
+  <si>
+    <t>3.3 沟通内容</t>
+  </si>
+  <si>
+    <t>定义与目标</t>
+  </si>
+  <si>
+    <t>在合适时间与方式产生、收集、处理、存储与交流项目信息</t>
+  </si>
+  <si>
+    <t>影响因素</t>
+  </si>
+  <si>
+    <t>识别影响因素</t>
+  </si>
+  <si>
+    <t>地位;个性;性别组合;沟通渠道</t>
+  </si>
+  <si>
+    <t>量化沟通成本</t>
+  </si>
+  <si>
+    <t>沟通渠道数=N(N-1)/2;规模与效率的平衡</t>
+  </si>
+  <si>
+    <t>规划沟通与例会</t>
+  </si>
+  <si>
+    <t>组内状态检查;评审与版本发布;问题讨论;周会与阶段评审</t>
+  </si>
+  <si>
+    <t>四、软件项目规划</t>
+  </si>
+  <si>
+    <t>1.5 项目活动-规划阶段</t>
+  </si>
+  <si>
+    <t>4.5 WBS</t>
+  </si>
+  <si>
+    <t>建立可执行计划</t>
+  </si>
+  <si>
+    <t>明确目的与范围;分解活动;估算规模/资源;制定进度与配套计划</t>
+  </si>
+  <si>
+    <t>4.1 定义与过程</t>
+  </si>
+  <si>
+    <t>软件项目规划</t>
+  </si>
+  <si>
+    <t>说清规划过程</t>
+  </si>
+  <si>
+    <t>目标/范围→WBS→规模与资源估算→计划编制</t>
+  </si>
+  <si>
+    <t>4.2 规模估算</t>
+  </si>
+  <si>
+    <t>4.3 成本估算</t>
+  </si>
+  <si>
+    <t>掌握两类估算法</t>
+  </si>
+  <si>
+    <t>代码行（LOC）与功能点（FP）</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -143,6 +1180,7 @@
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -151,6 +1189,7 @@
       <sz val="11"/>
       <color theme="0"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -159,6 +1198,7 @@
       <sz val="11"/>
       <color theme="0"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -172,6 +1212,39 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <color theme="1"/>
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
@@ -243,7 +1316,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -253,14 +1326,41 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -573,28 +1673,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:O111"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="7" width="11" customWidth="1"/>
-    <col min="8" max="15" width="15.59765625" customWidth="1"/>
+    <col min="8" max="15" width="15.58203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="129.94999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="4"/>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:15" ht="130" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="6"/>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -641,63 +1741,2295 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A3" t="s">
+    <row r="3" spans="1:15" ht="56" x14ac:dyDescent="0.3">
+      <c r="A3" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="13" t="s">
+        <v>194</v>
+      </c>
+      <c r="I3" s="13" t="s">
+        <v>195</v>
+      </c>
+      <c r="J3" s="13" t="s">
+        <v>196</v>
+      </c>
+      <c r="K3" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="M3" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="N3" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="O3" s="13" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="56" x14ac:dyDescent="0.3">
+      <c r="A4" s="3"/>
+      <c r="B4" s="13" t="s">
+        <v>199</v>
+      </c>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="I4" s="13" t="s">
+        <v>200</v>
+      </c>
+      <c r="J4" s="13" t="s">
+        <v>201</v>
+      </c>
+      <c r="K4" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="L4" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="M4" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="N4" s="13" t="s">
+        <v>202</v>
+      </c>
+      <c r="O4" s="13" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="42" x14ac:dyDescent="0.3">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="13" t="s">
+        <v>199</v>
+      </c>
+      <c r="I5" s="13" t="s">
+        <v>201</v>
+      </c>
+      <c r="J5" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="K5" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="L5" s="13" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="B4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="C5" t="s">
+      <c r="M5" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="N5" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="O5" s="13" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A6" s="3"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="13" t="s">
+        <v>207</v>
+      </c>
+      <c r="H6" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="K6" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="L6" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="M6" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="N6" s="13" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="42" x14ac:dyDescent="0.3">
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="13" t="s">
+        <v>208</v>
+      </c>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="I7" s="13" t="s">
+        <v>200</v>
+      </c>
+      <c r="J7" s="13" t="s">
+        <v>209</v>
+      </c>
+      <c r="K7" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="L7" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="M7" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="N7" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="O7" s="13" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="42" x14ac:dyDescent="0.3">
+      <c r="A8" s="3"/>
+      <c r="B8" s="13" t="s">
+        <v>212</v>
+      </c>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="13" t="s">
+        <v>199</v>
+      </c>
+      <c r="I8" s="13" t="s">
+        <v>201</v>
+      </c>
+      <c r="J8" s="13" t="s">
+        <v>213</v>
+      </c>
+      <c r="K8" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="L8" s="13" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="C6" t="s">
+      <c r="M8" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="H6" t="s">
+      <c r="N8" s="13" t="s">
+        <v>214</v>
+      </c>
+      <c r="O8" s="13" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" ht="56" x14ac:dyDescent="0.3">
+      <c r="A9" s="3"/>
+      <c r="B9" s="13" t="s">
+        <v>216</v>
+      </c>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="13" t="s">
+        <v>212</v>
+      </c>
+      <c r="I9" s="13" t="s">
+        <v>201</v>
+      </c>
+      <c r="J9" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="K9" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="L9" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="I6" t="s">
-        <v>19</v>
-      </c>
-      <c r="J6" t="s">
+      <c r="M9" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="N9" s="13" t="s">
+        <v>218</v>
+      </c>
+      <c r="O9" s="13" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" ht="42" x14ac:dyDescent="0.3">
+      <c r="A10" s="3"/>
+      <c r="B10" s="13" t="s">
+        <v>201</v>
+      </c>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="13" t="s">
+        <v>209</v>
+      </c>
+      <c r="I10" s="13" t="s">
+        <v>200</v>
+      </c>
+      <c r="J10" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="K10" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="L10" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="K6" t="s">
-        <v>21</v>
-      </c>
-      <c r="L6" t="s">
+      <c r="M10" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="N10" s="13" t="s">
+        <v>220</v>
+      </c>
+      <c r="O10" s="13" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" ht="42" x14ac:dyDescent="0.3">
+      <c r="A11" s="3"/>
+      <c r="B11" s="13" t="s">
+        <v>200</v>
+      </c>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="13" t="s">
+        <v>201</v>
+      </c>
+      <c r="I11" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="J11" s="13" t="s">
+        <v>222</v>
+      </c>
+      <c r="K11" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="L11" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="M6" t="s">
+      <c r="M11" s="13" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="C7" t="s">
+      <c r="N11" s="13" t="s">
+        <v>223</v>
+      </c>
+      <c r="O11" s="13" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" ht="28" x14ac:dyDescent="0.3">
+      <c r="A12" s="3"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="13" t="s">
+        <v>225</v>
+      </c>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="13" t="s">
+        <v>200</v>
+      </c>
+      <c r="I12" s="3"/>
+      <c r="J12" s="3"/>
+      <c r="K12" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="L12" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M12" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="N12" s="13" t="s">
+        <v>226</v>
+      </c>
+      <c r="O12" s="13" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" ht="56" x14ac:dyDescent="0.3">
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="13" t="s">
+        <v>228</v>
+      </c>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="13" t="s">
+        <v>200</v>
+      </c>
+      <c r="I13" s="13" t="s">
+        <v>229</v>
+      </c>
+      <c r="J13" s="13" t="s">
+        <v>230</v>
+      </c>
+      <c r="K13" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="L13" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M13" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="N13" s="13" t="s">
+        <v>231</v>
+      </c>
+      <c r="O13" s="13" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" ht="42" x14ac:dyDescent="0.3">
+      <c r="A14" s="3"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="13" t="s">
+        <v>229</v>
+      </c>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="13" t="s">
+        <v>228</v>
+      </c>
+      <c r="I14" s="13" t="s">
+        <v>233</v>
+      </c>
+      <c r="J14" s="13" t="s">
+        <v>234</v>
+      </c>
+      <c r="K14" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="L14" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M14" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="N14" s="13" t="s">
+        <v>235</v>
+      </c>
+      <c r="O14" s="13" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" ht="42" x14ac:dyDescent="0.3">
+      <c r="A15" s="3"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="13" t="s">
+        <v>233</v>
+      </c>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="13" t="s">
+        <v>229</v>
+      </c>
+      <c r="I15" s="3"/>
+      <c r="J15" s="3"/>
+      <c r="K15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="L15" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M15" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="N15" s="13" t="s">
+        <v>237</v>
+      </c>
+      <c r="O15" s="13" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" ht="42" x14ac:dyDescent="0.3">
+      <c r="A16" s="3"/>
+      <c r="B16" s="13" t="s">
+        <v>239</v>
+      </c>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="13" t="s">
+        <v>212</v>
+      </c>
+      <c r="I16" s="13" t="s">
+        <v>240</v>
+      </c>
+      <c r="J16" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="K16" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="L16" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="M16" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="N16" s="13" t="s">
+        <v>241</v>
+      </c>
+      <c r="O16" s="13" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" ht="42" x14ac:dyDescent="0.3">
+      <c r="A17" s="3"/>
+      <c r="B17" s="3"/>
+      <c r="C17" s="13" t="s">
+        <v>243</v>
+      </c>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="13" t="s">
+        <v>244</v>
+      </c>
+      <c r="I17" s="13" t="s">
+        <v>245</v>
+      </c>
+      <c r="J17" s="13" t="s">
+        <v>246</v>
+      </c>
+      <c r="K17" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="L17" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="M17" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="N17" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="O17" s="13" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" ht="42" x14ac:dyDescent="0.3">
+      <c r="A18" s="3"/>
+      <c r="B18" s="3"/>
+      <c r="C18" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="13" t="s">
+        <v>243</v>
+      </c>
+      <c r="I18" s="13" t="s">
+        <v>246</v>
+      </c>
+      <c r="J18" s="3"/>
+      <c r="K18" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="L18" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M18" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="N18" s="13" t="s">
+        <v>250</v>
+      </c>
+      <c r="O18" s="13" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" ht="56" x14ac:dyDescent="0.3">
+      <c r="A19" s="3"/>
+      <c r="B19" s="3"/>
+      <c r="C19" s="13" t="s">
+        <v>252</v>
+      </c>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="I19" s="13" t="s">
+        <v>245</v>
+      </c>
+      <c r="J19" s="13" t="s">
+        <v>253</v>
+      </c>
+      <c r="K19" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="L19" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="M19" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="N19" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="O19" s="13" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" ht="42" x14ac:dyDescent="0.3">
+      <c r="A20" s="3"/>
+      <c r="B20" s="3"/>
+      <c r="C20" s="13" t="s">
+        <v>245</v>
+      </c>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="13" t="s">
+        <v>252</v>
+      </c>
+      <c r="I20" s="13" t="s">
+        <v>256</v>
+      </c>
+      <c r="J20" s="3"/>
+      <c r="K20" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="L20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="M20" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="N20" s="13" t="s">
+        <v>257</v>
+      </c>
+      <c r="O20" s="13" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" ht="42" x14ac:dyDescent="0.3">
+      <c r="A21" s="3"/>
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="13" t="s">
+        <v>259</v>
+      </c>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="13" t="s">
+        <v>245</v>
+      </c>
+      <c r="I21" s="13" t="s">
+        <v>260</v>
+      </c>
+      <c r="J21" s="3"/>
+      <c r="K21" s="13" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="B8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="C9" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A10" t="s">
+      <c r="L21" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="M21" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="N21" s="13" t="s">
+        <v>261</v>
+      </c>
+      <c r="O21" s="13" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" ht="42" x14ac:dyDescent="0.3">
+      <c r="A22" s="3"/>
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="13" t="s">
+        <v>260</v>
+      </c>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="13" t="s">
+        <v>245</v>
+      </c>
+      <c r="I22" s="13" t="s">
+        <v>263</v>
+      </c>
+      <c r="J22" s="3"/>
+      <c r="K22" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="L22" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="M22" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="N22" s="13" t="s">
+        <v>261</v>
+      </c>
+      <c r="O22" s="13" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" ht="42" x14ac:dyDescent="0.3">
+      <c r="A23" s="3"/>
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="13" t="s">
+        <v>263</v>
+      </c>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="13" t="s">
+        <v>245</v>
+      </c>
+      <c r="I23" s="3"/>
+      <c r="J23" s="3"/>
+      <c r="K23" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="L23" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="M23" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="N23" s="13" t="s">
+        <v>261</v>
+      </c>
+      <c r="O23" s="13" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" ht="56" x14ac:dyDescent="0.3">
+      <c r="A24" s="3"/>
+      <c r="B24" s="13" t="s">
+        <v>266</v>
+      </c>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+      <c r="H24" s="13" t="s">
+        <v>244</v>
+      </c>
+      <c r="I24" s="13" t="s">
+        <v>267</v>
+      </c>
+      <c r="J24" s="13" t="s">
+        <v>268</v>
+      </c>
+      <c r="K24" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="L24" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="M24" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="N24" s="13" t="s">
+        <v>269</v>
+      </c>
+      <c r="O24" s="13" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" ht="28" x14ac:dyDescent="0.3">
+      <c r="A25" s="3"/>
+      <c r="B25" s="3"/>
+      <c r="C25" s="13" t="s">
+        <v>271</v>
+      </c>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+      <c r="H25" s="13" t="s">
+        <v>253</v>
+      </c>
+      <c r="I25" s="13" t="s">
+        <v>267</v>
+      </c>
+      <c r="J25" s="3"/>
+      <c r="K25" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="L25" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="M25" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="N25" s="13" t="s">
+        <v>272</v>
+      </c>
+      <c r="O25" s="13" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" ht="42" x14ac:dyDescent="0.3">
+      <c r="A26" s="3"/>
+      <c r="B26" s="3"/>
+      <c r="C26" s="13" t="s">
+        <v>267</v>
+      </c>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+      <c r="H26" s="13" t="s">
+        <v>271</v>
+      </c>
+      <c r="I26" s="13" t="s">
+        <v>268</v>
+      </c>
+      <c r="J26" s="3"/>
+      <c r="K26" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="L26" s="13" t="s">
         <v>20</v>
       </c>
+      <c r="M26" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="N26" s="13" t="s">
+        <v>274</v>
+      </c>
+      <c r="O26" s="13" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" ht="56" x14ac:dyDescent="0.3">
+      <c r="A27" s="3"/>
+      <c r="B27" s="3"/>
+      <c r="C27" s="13" t="s">
+        <v>268</v>
+      </c>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
+      <c r="H27" s="13" t="s">
+        <v>267</v>
+      </c>
+      <c r="I27" s="3"/>
+      <c r="J27" s="3"/>
+      <c r="K27" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="L27" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M27" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="N27" s="13" t="s">
+        <v>276</v>
+      </c>
+      <c r="O27" s="13" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" ht="56" x14ac:dyDescent="0.3">
+      <c r="A28" s="3"/>
+      <c r="B28" s="13" t="s">
+        <v>278</v>
+      </c>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="13" t="s">
+        <v>279</v>
+      </c>
+      <c r="I28" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="J28" s="13" t="s">
+        <v>280</v>
+      </c>
+      <c r="K28" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="L28" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M28" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="N28" s="13" t="s">
+        <v>281</v>
+      </c>
+      <c r="O28" s="13" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" ht="42" x14ac:dyDescent="0.3">
+      <c r="A29" s="3"/>
+      <c r="B29" s="3"/>
+      <c r="C29" s="13" t="s">
+        <v>283</v>
+      </c>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
+      <c r="H29" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="I29" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="J29" s="3"/>
+      <c r="K29" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="L29" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="M29" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="N29" s="13" t="s">
+        <v>285</v>
+      </c>
+      <c r="O29" s="13" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" ht="28" x14ac:dyDescent="0.3">
+      <c r="A30" s="3"/>
+      <c r="B30" s="3"/>
+      <c r="C30" s="13" t="s">
+        <v>287</v>
+      </c>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
+      <c r="H30" s="13" t="s">
+        <v>283</v>
+      </c>
+      <c r="I30" s="13" t="s">
+        <v>288</v>
+      </c>
+      <c r="J30" s="3"/>
+      <c r="K30" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="L30" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="M30" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="N30" s="13" t="s">
+        <v>289</v>
+      </c>
+      <c r="O30" s="13" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A31" s="3"/>
+      <c r="B31" s="13"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
+      <c r="H31" s="13"/>
+      <c r="I31" s="3"/>
+      <c r="J31" s="13"/>
+      <c r="K31" s="13"/>
+      <c r="L31" s="13"/>
+      <c r="M31" s="13"/>
+      <c r="N31" s="13"/>
+      <c r="O31" s="13"/>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A32" s="3"/>
+      <c r="B32" s="3"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3"/>
+      <c r="H32" s="13"/>
+      <c r="I32" s="3"/>
+      <c r="J32" s="3"/>
+      <c r="K32" s="13"/>
+      <c r="L32" s="13"/>
+      <c r="M32" s="13"/>
+      <c r="N32" s="13"/>
+      <c r="O32" s="13"/>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A33" s="3"/>
+      <c r="B33" s="13"/>
+      <c r="C33" s="3"/>
+      <c r="D33" s="3"/>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3"/>
+      <c r="H33" s="13"/>
+      <c r="I33" s="3"/>
+      <c r="J33" s="3"/>
+      <c r="K33" s="13"/>
+      <c r="L33" s="13"/>
+      <c r="M33" s="13"/>
+      <c r="N33" s="13"/>
+      <c r="O33" s="13"/>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A34" s="3"/>
+      <c r="B34" s="13"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3"/>
+      <c r="H34" s="13"/>
+      <c r="I34" s="3"/>
+      <c r="J34" s="13"/>
+      <c r="K34" s="13"/>
+      <c r="L34" s="13"/>
+      <c r="M34" s="13"/>
+      <c r="N34" s="13"/>
+      <c r="O34" s="13"/>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A35" s="3"/>
+      <c r="B35" s="3"/>
+      <c r="C35" s="13"/>
+      <c r="D35" s="3"/>
+      <c r="E35" s="3"/>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3"/>
+      <c r="H35" s="13"/>
+      <c r="I35" s="3"/>
+      <c r="J35" s="3"/>
+      <c r="K35" s="13"/>
+      <c r="L35" s="13"/>
+      <c r="M35" s="13"/>
+      <c r="N35" s="13"/>
+      <c r="O35" s="13"/>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A36" s="3"/>
+      <c r="B36" s="3"/>
+      <c r="C36" s="3"/>
+      <c r="D36" s="13"/>
+      <c r="E36" s="3"/>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3"/>
+      <c r="H36" s="13"/>
+      <c r="I36" s="13"/>
+      <c r="J36" s="3"/>
+      <c r="K36" s="13"/>
+      <c r="L36" s="13"/>
+      <c r="M36" s="13"/>
+      <c r="N36" s="13"/>
+      <c r="O36" s="13"/>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A37" s="3"/>
+      <c r="B37" s="3"/>
+      <c r="C37" s="3"/>
+      <c r="D37" s="13"/>
+      <c r="E37" s="3"/>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3"/>
+      <c r="H37" s="13"/>
+      <c r="I37" s="13"/>
+      <c r="J37" s="3"/>
+      <c r="K37" s="13"/>
+      <c r="L37" s="13"/>
+      <c r="M37" s="13"/>
+      <c r="N37" s="13"/>
+      <c r="O37" s="13"/>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A38" s="3"/>
+      <c r="B38" s="3"/>
+      <c r="C38" s="3"/>
+      <c r="D38" s="13"/>
+      <c r="E38" s="3"/>
+      <c r="F38" s="3"/>
+      <c r="G38" s="3"/>
+      <c r="H38" s="13"/>
+      <c r="I38" s="13"/>
+      <c r="J38" s="3"/>
+      <c r="K38" s="13"/>
+      <c r="L38" s="13"/>
+      <c r="M38" s="13"/>
+      <c r="N38" s="13"/>
+      <c r="O38" s="13"/>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A39" s="3"/>
+      <c r="B39" s="3"/>
+      <c r="C39" s="3"/>
+      <c r="D39" s="13"/>
+      <c r="E39" s="3"/>
+      <c r="F39" s="3"/>
+      <c r="G39" s="3"/>
+      <c r="H39" s="13"/>
+      <c r="I39" s="13"/>
+      <c r="J39" s="3"/>
+      <c r="K39" s="13"/>
+      <c r="L39" s="13"/>
+      <c r="M39" s="13"/>
+      <c r="N39" s="13"/>
+      <c r="O39" s="13"/>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A40" s="3"/>
+      <c r="B40" s="3"/>
+      <c r="C40" s="3"/>
+      <c r="D40" s="13"/>
+      <c r="E40" s="3"/>
+      <c r="F40" s="3"/>
+      <c r="G40" s="3"/>
+      <c r="H40" s="13"/>
+      <c r="I40" s="13"/>
+      <c r="J40" s="3"/>
+      <c r="K40" s="13"/>
+      <c r="L40" s="13"/>
+      <c r="M40" s="13"/>
+      <c r="N40" s="13"/>
+      <c r="O40" s="13"/>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A41" s="3"/>
+      <c r="B41" s="3"/>
+      <c r="C41" s="3"/>
+      <c r="D41" s="13"/>
+      <c r="E41" s="3"/>
+      <c r="F41" s="3"/>
+      <c r="G41" s="3"/>
+      <c r="H41" s="13"/>
+      <c r="I41" s="3"/>
+      <c r="J41" s="3"/>
+      <c r="K41" s="13"/>
+      <c r="L41" s="13"/>
+      <c r="M41" s="13"/>
+      <c r="N41" s="13"/>
+      <c r="O41" s="13"/>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A42" s="3"/>
+      <c r="B42" s="3"/>
+      <c r="C42" s="13"/>
+      <c r="D42" s="3"/>
+      <c r="E42" s="3"/>
+      <c r="F42" s="3"/>
+      <c r="G42" s="3"/>
+      <c r="H42" s="13"/>
+      <c r="I42" s="3"/>
+      <c r="J42" s="3"/>
+      <c r="K42" s="13"/>
+      <c r="L42" s="13"/>
+      <c r="M42" s="13"/>
+      <c r="N42" s="13"/>
+      <c r="O42" s="13"/>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A43" s="3"/>
+      <c r="B43" s="3"/>
+      <c r="C43" s="3"/>
+      <c r="D43" s="13"/>
+      <c r="E43" s="3"/>
+      <c r="F43" s="3"/>
+      <c r="G43" s="3"/>
+      <c r="H43" s="13"/>
+      <c r="I43" s="13"/>
+      <c r="J43" s="3"/>
+      <c r="K43" s="13"/>
+      <c r="L43" s="13"/>
+      <c r="M43" s="13"/>
+      <c r="N43" s="13"/>
+      <c r="O43" s="13"/>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A44" s="3"/>
+      <c r="B44" s="3"/>
+      <c r="C44" s="3"/>
+      <c r="D44" s="13"/>
+      <c r="E44" s="3"/>
+      <c r="F44" s="3"/>
+      <c r="G44" s="3"/>
+      <c r="H44" s="13"/>
+      <c r="I44" s="13"/>
+      <c r="J44" s="3"/>
+      <c r="K44" s="13"/>
+      <c r="L44" s="13"/>
+      <c r="M44" s="13"/>
+      <c r="N44" s="13"/>
+      <c r="O44" s="13"/>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A45" s="3"/>
+      <c r="B45" s="3"/>
+      <c r="C45" s="3"/>
+      <c r="D45" s="13"/>
+      <c r="E45" s="3"/>
+      <c r="F45" s="3"/>
+      <c r="G45" s="3"/>
+      <c r="H45" s="13"/>
+      <c r="I45" s="13"/>
+      <c r="J45" s="3"/>
+      <c r="K45" s="13"/>
+      <c r="L45" s="13"/>
+      <c r="M45" s="13"/>
+      <c r="N45" s="13"/>
+      <c r="O45" s="13"/>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A46" s="3"/>
+      <c r="B46" s="13"/>
+      <c r="C46" s="3"/>
+      <c r="D46" s="3"/>
+      <c r="E46" s="3"/>
+      <c r="F46" s="3"/>
+      <c r="G46" s="3"/>
+      <c r="H46" s="13"/>
+      <c r="I46" s="3"/>
+      <c r="J46" s="3"/>
+      <c r="K46" s="13"/>
+      <c r="L46" s="13"/>
+      <c r="M46" s="13"/>
+      <c r="N46" s="13"/>
+      <c r="O46" s="13"/>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A47" s="3"/>
+      <c r="B47" s="3"/>
+      <c r="C47" s="13"/>
+      <c r="D47" s="3"/>
+      <c r="E47" s="3"/>
+      <c r="F47" s="3"/>
+      <c r="G47" s="3"/>
+      <c r="H47" s="13"/>
+      <c r="I47" s="3"/>
+      <c r="J47" s="3"/>
+      <c r="K47" s="13"/>
+      <c r="L47" s="13"/>
+      <c r="M47" s="13"/>
+      <c r="N47" s="13"/>
+      <c r="O47" s="13"/>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A48" s="3"/>
+      <c r="B48" s="3"/>
+      <c r="C48" s="13"/>
+      <c r="D48" s="3"/>
+      <c r="E48" s="3"/>
+      <c r="F48" s="3"/>
+      <c r="G48" s="3"/>
+      <c r="H48" s="13"/>
+      <c r="I48" s="3"/>
+      <c r="J48" s="3"/>
+      <c r="K48" s="13"/>
+      <c r="L48" s="13"/>
+      <c r="M48" s="13"/>
+      <c r="N48" s="13"/>
+      <c r="O48" s="13"/>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A49" s="3"/>
+      <c r="B49" s="13"/>
+      <c r="C49" s="3"/>
+      <c r="D49" s="3"/>
+      <c r="E49" s="3"/>
+      <c r="F49" s="3"/>
+      <c r="G49" s="3"/>
+      <c r="H49" s="13"/>
+      <c r="I49" s="3"/>
+      <c r="J49" s="3"/>
+      <c r="K49" s="13"/>
+      <c r="L49" s="13"/>
+      <c r="M49" s="13"/>
+      <c r="N49" s="13"/>
+      <c r="O49" s="13"/>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A50" s="13"/>
+      <c r="B50" s="3"/>
+      <c r="C50" s="3"/>
+      <c r="D50" s="3"/>
+      <c r="E50" s="3"/>
+      <c r="F50" s="3"/>
+      <c r="G50" s="3"/>
+      <c r="H50" s="13"/>
+      <c r="I50" s="13"/>
+      <c r="J50" s="3"/>
+      <c r="K50" s="13"/>
+      <c r="L50" s="13"/>
+      <c r="M50" s="13"/>
+      <c r="N50" s="13"/>
+      <c r="O50" s="13"/>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A51" s="3"/>
+      <c r="B51" s="13"/>
+      <c r="C51" s="3"/>
+      <c r="D51" s="3"/>
+      <c r="E51" s="3"/>
+      <c r="F51" s="3"/>
+      <c r="G51" s="3"/>
+      <c r="H51" s="13"/>
+      <c r="I51" s="13"/>
+      <c r="J51" s="13"/>
+      <c r="K51" s="13"/>
+      <c r="L51" s="13"/>
+      <c r="M51" s="13"/>
+      <c r="N51" s="13"/>
+      <c r="O51" s="13"/>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A52" s="3"/>
+      <c r="B52" s="3"/>
+      <c r="C52" s="13"/>
+      <c r="D52" s="3"/>
+      <c r="E52" s="3"/>
+      <c r="F52" s="3"/>
+      <c r="G52" s="3"/>
+      <c r="H52" s="13"/>
+      <c r="I52" s="13"/>
+      <c r="J52" s="13"/>
+      <c r="K52" s="13"/>
+      <c r="L52" s="13"/>
+      <c r="M52" s="13"/>
+      <c r="N52" s="13"/>
+      <c r="O52" s="13"/>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A53" s="3"/>
+      <c r="B53" s="3"/>
+      <c r="C53" s="13"/>
+      <c r="D53" s="3"/>
+      <c r="E53" s="3"/>
+      <c r="F53" s="3"/>
+      <c r="G53" s="3"/>
+      <c r="H53" s="13"/>
+      <c r="I53" s="3"/>
+      <c r="J53" s="3"/>
+      <c r="K53" s="13"/>
+      <c r="L53" s="13"/>
+      <c r="M53" s="13"/>
+      <c r="N53" s="13"/>
+      <c r="O53" s="13"/>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A54" s="3"/>
+      <c r="B54" s="3"/>
+      <c r="C54" s="13"/>
+      <c r="D54" s="3"/>
+      <c r="E54" s="3"/>
+      <c r="F54" s="3"/>
+      <c r="G54" s="3"/>
+      <c r="H54" s="13"/>
+      <c r="I54" s="13"/>
+      <c r="J54" s="3"/>
+      <c r="K54" s="13"/>
+      <c r="L54" s="13"/>
+      <c r="M54" s="13"/>
+      <c r="N54" s="13"/>
+      <c r="O54" s="13"/>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A55" s="3"/>
+      <c r="B55" s="13"/>
+      <c r="C55" s="3"/>
+      <c r="D55" s="3"/>
+      <c r="E55" s="3"/>
+      <c r="F55" s="3"/>
+      <c r="G55" s="3"/>
+      <c r="H55" s="13"/>
+      <c r="I55" s="13"/>
+      <c r="J55" s="3"/>
+      <c r="K55" s="13"/>
+      <c r="L55" s="13"/>
+      <c r="M55" s="13"/>
+      <c r="N55" s="13"/>
+      <c r="O55" s="13"/>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A56" s="3"/>
+      <c r="B56" s="3"/>
+      <c r="C56" s="13"/>
+      <c r="D56" s="3"/>
+      <c r="E56" s="3"/>
+      <c r="F56" s="3"/>
+      <c r="G56" s="3"/>
+      <c r="H56" s="13"/>
+      <c r="I56" s="13"/>
+      <c r="J56" s="3"/>
+      <c r="K56" s="13"/>
+      <c r="L56" s="13"/>
+      <c r="M56" s="13"/>
+      <c r="N56" s="13"/>
+      <c r="O56" s="13"/>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A57" s="3"/>
+      <c r="B57" s="3"/>
+      <c r="C57" s="13"/>
+      <c r="D57" s="3"/>
+      <c r="E57" s="3"/>
+      <c r="F57" s="3"/>
+      <c r="G57" s="3"/>
+      <c r="H57" s="13"/>
+      <c r="I57" s="3"/>
+      <c r="J57" s="3"/>
+      <c r="K57" s="13"/>
+      <c r="L57" s="13"/>
+      <c r="M57" s="13"/>
+      <c r="N57" s="13"/>
+      <c r="O57" s="13"/>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A58" s="3"/>
+      <c r="B58" s="3"/>
+      <c r="C58" s="13"/>
+      <c r="D58" s="3"/>
+      <c r="E58" s="3"/>
+      <c r="F58" s="3"/>
+      <c r="G58" s="3"/>
+      <c r="H58" s="13"/>
+      <c r="I58" s="13"/>
+      <c r="J58" s="3"/>
+      <c r="K58" s="13"/>
+      <c r="L58" s="13"/>
+      <c r="M58" s="13"/>
+      <c r="N58" s="13"/>
+      <c r="O58" s="13"/>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A59" s="3"/>
+      <c r="B59" s="3"/>
+      <c r="C59" s="13"/>
+      <c r="D59" s="3"/>
+      <c r="E59" s="3"/>
+      <c r="F59" s="3"/>
+      <c r="G59" s="3"/>
+      <c r="H59" s="13"/>
+      <c r="I59" s="13"/>
+      <c r="J59" s="3"/>
+      <c r="K59" s="13"/>
+      <c r="L59" s="13"/>
+      <c r="M59" s="13"/>
+      <c r="N59" s="13"/>
+      <c r="O59" s="13"/>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A60" s="3"/>
+      <c r="B60" s="3"/>
+      <c r="C60" s="13"/>
+      <c r="D60" s="3"/>
+      <c r="E60" s="3"/>
+      <c r="F60" s="3"/>
+      <c r="G60" s="3"/>
+      <c r="H60" s="13"/>
+      <c r="I60" s="13"/>
+      <c r="J60" s="3"/>
+      <c r="K60" s="13"/>
+      <c r="L60" s="13"/>
+      <c r="M60" s="13"/>
+      <c r="N60" s="13"/>
+      <c r="O60" s="13"/>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A61" s="3"/>
+      <c r="B61" s="13"/>
+      <c r="C61" s="3"/>
+      <c r="D61" s="3"/>
+      <c r="E61" s="3"/>
+      <c r="F61" s="3"/>
+      <c r="G61" s="3"/>
+      <c r="H61" s="13"/>
+      <c r="I61" s="13"/>
+      <c r="J61" s="13"/>
+      <c r="K61" s="13"/>
+      <c r="L61" s="13"/>
+      <c r="M61" s="13"/>
+      <c r="N61" s="13"/>
+      <c r="O61" s="13"/>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A62" s="3"/>
+      <c r="B62" s="3"/>
+      <c r="C62" s="13"/>
+      <c r="D62" s="3"/>
+      <c r="E62" s="3"/>
+      <c r="F62" s="3"/>
+      <c r="G62" s="3"/>
+      <c r="H62" s="13"/>
+      <c r="I62" s="3"/>
+      <c r="J62" s="3"/>
+      <c r="K62" s="13"/>
+      <c r="L62" s="13"/>
+      <c r="M62" s="13"/>
+      <c r="N62" s="13"/>
+      <c r="O62" s="13"/>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A63" s="3"/>
+      <c r="B63" s="3"/>
+      <c r="C63" s="13"/>
+      <c r="D63" s="3"/>
+      <c r="E63" s="3"/>
+      <c r="F63" s="3"/>
+      <c r="G63" s="3"/>
+      <c r="H63" s="13"/>
+      <c r="I63" s="13"/>
+      <c r="J63" s="3"/>
+      <c r="K63" s="13"/>
+      <c r="L63" s="13"/>
+      <c r="M63" s="13"/>
+      <c r="N63" s="13"/>
+      <c r="O63" s="13"/>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A64" s="3"/>
+      <c r="B64" s="3"/>
+      <c r="C64" s="13"/>
+      <c r="D64" s="3"/>
+      <c r="E64" s="3"/>
+      <c r="F64" s="3"/>
+      <c r="G64" s="3"/>
+      <c r="H64" s="13"/>
+      <c r="I64" s="13"/>
+      <c r="J64" s="3"/>
+      <c r="K64" s="13"/>
+      <c r="L64" s="13"/>
+      <c r="M64" s="13"/>
+      <c r="N64" s="13"/>
+      <c r="O64" s="13"/>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A65" s="3"/>
+      <c r="B65" s="3"/>
+      <c r="C65" s="13"/>
+      <c r="D65" s="3"/>
+      <c r="E65" s="3"/>
+      <c r="F65" s="3"/>
+      <c r="G65" s="3"/>
+      <c r="H65" s="13"/>
+      <c r="I65" s="13"/>
+      <c r="J65" s="3"/>
+      <c r="K65" s="13"/>
+      <c r="L65" s="13"/>
+      <c r="M65" s="13"/>
+      <c r="N65" s="13"/>
+      <c r="O65" s="13"/>
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A66" s="3"/>
+      <c r="B66" s="13"/>
+      <c r="C66" s="3"/>
+      <c r="D66" s="3"/>
+      <c r="E66" s="3"/>
+      <c r="F66" s="3"/>
+      <c r="G66" s="3"/>
+      <c r="H66" s="13"/>
+      <c r="I66" s="13"/>
+      <c r="J66" s="3"/>
+      <c r="K66" s="13"/>
+      <c r="L66" s="13"/>
+      <c r="M66" s="13"/>
+      <c r="N66" s="13"/>
+      <c r="O66" s="13"/>
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A67" s="3"/>
+      <c r="B67" s="13"/>
+      <c r="C67" s="3"/>
+      <c r="D67" s="3"/>
+      <c r="E67" s="3"/>
+      <c r="F67" s="3"/>
+      <c r="G67" s="3"/>
+      <c r="H67" s="13"/>
+      <c r="I67" s="13"/>
+      <c r="J67" s="3"/>
+      <c r="K67" s="13"/>
+      <c r="L67" s="13"/>
+      <c r="M67" s="13"/>
+      <c r="N67" s="13"/>
+      <c r="O67" s="13"/>
+    </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A68" s="3"/>
+      <c r="B68" s="3"/>
+      <c r="C68" s="13"/>
+      <c r="D68" s="3"/>
+      <c r="E68" s="3"/>
+      <c r="F68" s="3"/>
+      <c r="G68" s="3"/>
+      <c r="H68" s="13"/>
+      <c r="I68" s="3"/>
+      <c r="J68" s="3"/>
+      <c r="K68" s="13"/>
+      <c r="L68" s="13"/>
+      <c r="M68" s="13"/>
+      <c r="N68" s="13"/>
+      <c r="O68" s="13"/>
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A69" s="3"/>
+      <c r="B69" s="3"/>
+      <c r="C69" s="13"/>
+      <c r="D69" s="3"/>
+      <c r="E69" s="3"/>
+      <c r="F69" s="3"/>
+      <c r="G69" s="3"/>
+      <c r="H69" s="13"/>
+      <c r="I69" s="3"/>
+      <c r="J69" s="3"/>
+      <c r="K69" s="13"/>
+      <c r="L69" s="13"/>
+      <c r="M69" s="13"/>
+      <c r="N69" s="13"/>
+      <c r="O69" s="13"/>
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A70" s="3"/>
+      <c r="B70" s="3"/>
+      <c r="C70" s="13"/>
+      <c r="D70" s="3"/>
+      <c r="E70" s="3"/>
+      <c r="F70" s="3"/>
+      <c r="G70" s="3"/>
+      <c r="H70" s="13"/>
+      <c r="I70" s="3"/>
+      <c r="J70" s="3"/>
+      <c r="K70" s="13"/>
+      <c r="L70" s="13"/>
+      <c r="M70" s="13"/>
+      <c r="N70" s="13"/>
+      <c r="O70" s="13"/>
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A71" s="3"/>
+      <c r="B71" s="3"/>
+      <c r="C71" s="13"/>
+      <c r="D71" s="3"/>
+      <c r="E71" s="3"/>
+      <c r="F71" s="3"/>
+      <c r="G71" s="3"/>
+      <c r="H71" s="13"/>
+      <c r="I71" s="3"/>
+      <c r="J71" s="3"/>
+      <c r="K71" s="13"/>
+      <c r="L71" s="13"/>
+      <c r="M71" s="13"/>
+      <c r="N71" s="13"/>
+      <c r="O71" s="13"/>
+    </row>
+    <row r="72" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A72" s="3"/>
+      <c r="B72" s="13"/>
+      <c r="C72" s="3"/>
+      <c r="D72" s="3"/>
+      <c r="E72" s="3"/>
+      <c r="F72" s="3"/>
+      <c r="G72" s="3"/>
+      <c r="H72" s="13"/>
+      <c r="I72" s="3"/>
+      <c r="J72" s="3"/>
+      <c r="K72" s="13"/>
+      <c r="L72" s="13"/>
+      <c r="M72" s="13"/>
+      <c r="N72" s="13"/>
+      <c r="O72" s="13"/>
+    </row>
+    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A73" s="3"/>
+      <c r="B73" s="3"/>
+      <c r="C73" s="13"/>
+      <c r="D73" s="3"/>
+      <c r="E73" s="3"/>
+      <c r="F73" s="3"/>
+      <c r="G73" s="3"/>
+      <c r="H73" s="13"/>
+      <c r="I73" s="3"/>
+      <c r="J73" s="3"/>
+      <c r="K73" s="13"/>
+      <c r="L73" s="13"/>
+      <c r="M73" s="13"/>
+      <c r="N73" s="13"/>
+      <c r="O73" s="13"/>
+    </row>
+    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A74" s="3"/>
+      <c r="B74" s="3"/>
+      <c r="C74" s="13"/>
+      <c r="D74" s="3"/>
+      <c r="E74" s="3"/>
+      <c r="F74" s="3"/>
+      <c r="G74" s="3"/>
+      <c r="H74" s="13"/>
+      <c r="I74" s="3"/>
+      <c r="J74" s="3"/>
+      <c r="K74" s="13"/>
+      <c r="L74" s="13"/>
+      <c r="M74" s="13"/>
+      <c r="N74" s="13"/>
+      <c r="O74" s="13"/>
+    </row>
+    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A75" s="3"/>
+      <c r="B75" s="3"/>
+      <c r="C75" s="13"/>
+      <c r="D75" s="3"/>
+      <c r="E75" s="3"/>
+      <c r="F75" s="3"/>
+      <c r="G75" s="3"/>
+      <c r="H75" s="13"/>
+      <c r="I75" s="3"/>
+      <c r="J75" s="3"/>
+      <c r="K75" s="13"/>
+      <c r="L75" s="13"/>
+      <c r="M75" s="13"/>
+      <c r="N75" s="13"/>
+      <c r="O75" s="13"/>
+    </row>
+    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A76" s="3"/>
+      <c r="B76" s="13"/>
+      <c r="C76" s="3"/>
+      <c r="D76" s="3"/>
+      <c r="E76" s="3"/>
+      <c r="F76" s="3"/>
+      <c r="G76" s="3"/>
+      <c r="H76" s="13"/>
+      <c r="I76" s="13"/>
+      <c r="J76" s="3"/>
+      <c r="K76" s="13"/>
+      <c r="L76" s="13"/>
+      <c r="M76" s="13"/>
+      <c r="N76" s="13"/>
+      <c r="O76" s="13"/>
+    </row>
+    <row r="77" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A77" s="3"/>
+      <c r="B77" s="3"/>
+      <c r="C77" s="13"/>
+      <c r="D77" s="3"/>
+      <c r="E77" s="3"/>
+      <c r="F77" s="3"/>
+      <c r="G77" s="3"/>
+      <c r="H77" s="13"/>
+      <c r="I77" s="3"/>
+      <c r="J77" s="3"/>
+      <c r="K77" s="13"/>
+      <c r="L77" s="13"/>
+      <c r="M77" s="13"/>
+      <c r="N77" s="13"/>
+      <c r="O77" s="13"/>
+    </row>
+    <row r="78" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A78" s="3"/>
+      <c r="B78" s="3"/>
+      <c r="C78" s="13"/>
+      <c r="D78" s="3"/>
+      <c r="E78" s="3"/>
+      <c r="F78" s="3"/>
+      <c r="G78" s="3"/>
+      <c r="H78" s="13"/>
+      <c r="I78" s="3"/>
+      <c r="J78" s="3"/>
+      <c r="K78" s="13"/>
+      <c r="L78" s="13"/>
+      <c r="M78" s="13"/>
+      <c r="N78" s="13"/>
+      <c r="O78" s="13"/>
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A79" s="3"/>
+      <c r="B79" s="13"/>
+      <c r="C79" s="3"/>
+      <c r="D79" s="3"/>
+      <c r="E79" s="3"/>
+      <c r="F79" s="3"/>
+      <c r="G79" s="3"/>
+      <c r="H79" s="13"/>
+      <c r="I79" s="3"/>
+      <c r="J79" s="3"/>
+      <c r="K79" s="13"/>
+      <c r="L79" s="13"/>
+      <c r="M79" s="13"/>
+      <c r="N79" s="13"/>
+      <c r="O79" s="13"/>
+    </row>
+    <row r="80" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A80" s="3"/>
+      <c r="B80" s="3"/>
+      <c r="C80" s="13"/>
+      <c r="D80" s="3"/>
+      <c r="E80" s="3"/>
+      <c r="F80" s="3"/>
+      <c r="G80" s="3"/>
+      <c r="H80" s="13"/>
+      <c r="I80" s="3"/>
+      <c r="J80" s="3"/>
+      <c r="K80" s="13"/>
+      <c r="L80" s="13"/>
+      <c r="M80" s="13"/>
+      <c r="N80" s="13"/>
+      <c r="O80" s="13"/>
+    </row>
+    <row r="81" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A81" s="3"/>
+      <c r="B81" s="3"/>
+      <c r="C81" s="13"/>
+      <c r="D81" s="3"/>
+      <c r="E81" s="3"/>
+      <c r="F81" s="3"/>
+      <c r="G81" s="3"/>
+      <c r="H81" s="13"/>
+      <c r="I81" s="3"/>
+      <c r="J81" s="3"/>
+      <c r="K81" s="13"/>
+      <c r="L81" s="13"/>
+      <c r="M81" s="13"/>
+      <c r="N81" s="13"/>
+      <c r="O81" s="13"/>
+    </row>
+    <row r="82" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A82" s="3"/>
+      <c r="B82" s="13"/>
+      <c r="C82" s="3"/>
+      <c r="D82" s="3"/>
+      <c r="E82" s="3"/>
+      <c r="F82" s="3"/>
+      <c r="G82" s="3"/>
+      <c r="H82" s="13"/>
+      <c r="I82" s="3"/>
+      <c r="J82" s="3"/>
+      <c r="K82" s="13"/>
+      <c r="L82" s="13"/>
+      <c r="M82" s="13"/>
+      <c r="N82" s="13"/>
+      <c r="O82" s="13"/>
+    </row>
+    <row r="83" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A83" s="3"/>
+      <c r="B83" s="3"/>
+      <c r="C83" s="13"/>
+      <c r="D83" s="3"/>
+      <c r="E83" s="3"/>
+      <c r="F83" s="3"/>
+      <c r="G83" s="3"/>
+      <c r="H83" s="13"/>
+      <c r="I83" s="3"/>
+      <c r="J83" s="3"/>
+      <c r="K83" s="13"/>
+      <c r="L83" s="13"/>
+      <c r="M83" s="13"/>
+      <c r="N83" s="13"/>
+      <c r="O83" s="13"/>
+    </row>
+    <row r="84" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A84" s="3"/>
+      <c r="B84" s="3"/>
+      <c r="C84" s="13"/>
+      <c r="D84" s="3"/>
+      <c r="E84" s="3"/>
+      <c r="F84" s="3"/>
+      <c r="G84" s="3"/>
+      <c r="H84" s="13"/>
+      <c r="I84" s="3"/>
+      <c r="J84" s="3"/>
+      <c r="K84" s="13"/>
+      <c r="L84" s="13"/>
+      <c r="M84" s="13"/>
+      <c r="N84" s="13"/>
+      <c r="O84" s="13"/>
+    </row>
+    <row r="85" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A85" s="3"/>
+      <c r="B85" s="13"/>
+      <c r="C85" s="3"/>
+      <c r="D85" s="3"/>
+      <c r="E85" s="3"/>
+      <c r="F85" s="3"/>
+      <c r="G85" s="3"/>
+      <c r="H85" s="13"/>
+      <c r="I85" s="3"/>
+      <c r="J85" s="3"/>
+      <c r="K85" s="13"/>
+      <c r="L85" s="13"/>
+      <c r="M85" s="13"/>
+      <c r="N85" s="13"/>
+      <c r="O85" s="13"/>
+    </row>
+    <row r="86" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A86" s="3"/>
+      <c r="B86" s="3"/>
+      <c r="C86" s="13"/>
+      <c r="D86" s="3"/>
+      <c r="E86" s="3"/>
+      <c r="F86" s="3"/>
+      <c r="G86" s="3"/>
+      <c r="H86" s="13"/>
+      <c r="I86" s="3"/>
+      <c r="J86" s="3"/>
+      <c r="K86" s="13"/>
+      <c r="L86" s="13"/>
+      <c r="M86" s="13"/>
+      <c r="N86" s="13"/>
+      <c r="O86" s="13"/>
+    </row>
+    <row r="87" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A87" s="3"/>
+      <c r="B87" s="3"/>
+      <c r="C87" s="13"/>
+      <c r="D87" s="3"/>
+      <c r="E87" s="3"/>
+      <c r="F87" s="3"/>
+      <c r="G87" s="3"/>
+      <c r="H87" s="13"/>
+      <c r="I87" s="3"/>
+      <c r="J87" s="3"/>
+      <c r="K87" s="13"/>
+      <c r="L87" s="13"/>
+      <c r="M87" s="13"/>
+      <c r="N87" s="13"/>
+      <c r="O87" s="13"/>
+    </row>
+    <row r="88" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A88" s="3"/>
+      <c r="B88" s="3"/>
+      <c r="C88" s="13"/>
+      <c r="D88" s="3"/>
+      <c r="E88" s="3"/>
+      <c r="F88" s="3"/>
+      <c r="G88" s="3"/>
+      <c r="H88" s="13"/>
+      <c r="I88" s="3"/>
+      <c r="J88" s="3"/>
+      <c r="K88" s="13"/>
+      <c r="L88" s="13"/>
+      <c r="M88" s="13"/>
+      <c r="N88" s="13"/>
+      <c r="O88" s="13"/>
+    </row>
+    <row r="89" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A89" s="3"/>
+      <c r="B89" s="3"/>
+      <c r="C89" s="13"/>
+      <c r="D89" s="3"/>
+      <c r="E89" s="3"/>
+      <c r="F89" s="3"/>
+      <c r="G89" s="3"/>
+      <c r="H89" s="13"/>
+      <c r="I89" s="3"/>
+      <c r="J89" s="3"/>
+      <c r="K89" s="13"/>
+      <c r="L89" s="13"/>
+      <c r="M89" s="13"/>
+      <c r="N89" s="13"/>
+      <c r="O89" s="13"/>
+    </row>
+    <row r="90" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A90" s="3"/>
+      <c r="B90" s="13"/>
+      <c r="C90" s="3"/>
+      <c r="D90" s="3"/>
+      <c r="E90" s="3"/>
+      <c r="F90" s="3"/>
+      <c r="G90" s="3"/>
+      <c r="H90" s="13"/>
+      <c r="I90" s="3"/>
+      <c r="J90" s="3"/>
+      <c r="K90" s="13"/>
+      <c r="L90" s="13"/>
+      <c r="M90" s="13"/>
+      <c r="N90" s="13"/>
+      <c r="O90" s="13"/>
+    </row>
+    <row r="91" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A91" s="3"/>
+      <c r="B91" s="3"/>
+      <c r="C91" s="13"/>
+      <c r="D91" s="3"/>
+      <c r="E91" s="3"/>
+      <c r="F91" s="3"/>
+      <c r="G91" s="3"/>
+      <c r="H91" s="13"/>
+      <c r="I91" s="3"/>
+      <c r="J91" s="3"/>
+      <c r="K91" s="13"/>
+      <c r="L91" s="13"/>
+      <c r="M91" s="13"/>
+      <c r="N91" s="13"/>
+      <c r="O91" s="13"/>
+    </row>
+    <row r="92" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A92" s="3"/>
+      <c r="B92" s="13"/>
+      <c r="C92" s="3"/>
+      <c r="D92" s="3"/>
+      <c r="E92" s="3"/>
+      <c r="F92" s="3"/>
+      <c r="G92" s="3"/>
+      <c r="H92" s="13"/>
+      <c r="I92" s="3"/>
+      <c r="J92" s="3"/>
+      <c r="K92" s="13"/>
+      <c r="L92" s="13"/>
+      <c r="M92" s="13"/>
+      <c r="N92" s="13"/>
+      <c r="O92" s="13"/>
+    </row>
+    <row r="93" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A93" s="3"/>
+      <c r="B93" s="3"/>
+      <c r="C93" s="3"/>
+      <c r="D93" s="3"/>
+      <c r="E93" s="3"/>
+      <c r="F93" s="3"/>
+      <c r="G93" s="3"/>
+      <c r="H93" s="3"/>
+      <c r="I93" s="3"/>
+      <c r="J93" s="3"/>
+      <c r="K93" s="3"/>
+      <c r="L93" s="3"/>
+      <c r="M93" s="3"/>
+      <c r="N93" s="3"/>
+      <c r="O93" s="3"/>
+    </row>
+    <row r="94" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A94" s="3"/>
+      <c r="B94" s="3"/>
+      <c r="D94" s="3"/>
+      <c r="E94" s="3"/>
+      <c r="F94" s="3"/>
+      <c r="G94" s="3"/>
+      <c r="H94" s="3"/>
+      <c r="I94" s="3"/>
+      <c r="J94" s="3"/>
+      <c r="K94" s="3"/>
+      <c r="L94" s="3"/>
+      <c r="M94" s="3"/>
+      <c r="N94" s="3"/>
+      <c r="O94" s="3"/>
+    </row>
+    <row r="95" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A95" s="3"/>
+      <c r="B95" s="3"/>
+      <c r="C95" s="3"/>
+      <c r="D95" s="3"/>
+      <c r="E95" s="3"/>
+      <c r="F95" s="3"/>
+      <c r="G95" s="3"/>
+      <c r="H95" s="3"/>
+      <c r="I95" s="3"/>
+      <c r="J95" s="3"/>
+      <c r="K95" s="3"/>
+      <c r="L95" s="3"/>
+      <c r="M95" s="3"/>
+      <c r="N95" s="3"/>
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A96" s="3"/>
+      <c r="B96" s="3"/>
+      <c r="D96" s="3"/>
+      <c r="E96" s="3"/>
+      <c r="F96" s="3"/>
+      <c r="G96" s="3"/>
+      <c r="H96" s="3"/>
+      <c r="I96" s="3"/>
+      <c r="J96" s="3"/>
+      <c r="K96" s="3"/>
+      <c r="L96" s="3"/>
+      <c r="M96" s="3"/>
+      <c r="N96" s="3"/>
+      <c r="O96" s="3"/>
+    </row>
+    <row r="97" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A97" s="3"/>
+      <c r="B97" s="3"/>
+      <c r="C97" s="3"/>
+      <c r="D97" s="3"/>
+      <c r="E97" s="3"/>
+      <c r="F97" s="3"/>
+      <c r="G97" s="3"/>
+      <c r="H97" s="3"/>
+      <c r="I97" s="3"/>
+      <c r="J97" s="3"/>
+      <c r="K97" s="3"/>
+      <c r="L97" s="3"/>
+      <c r="M97" s="3"/>
+      <c r="N97" s="3"/>
+      <c r="O97" s="3"/>
+    </row>
+    <row r="98" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A98" s="3"/>
+      <c r="B98" s="3"/>
+      <c r="C98" s="3"/>
+      <c r="D98" s="3"/>
+      <c r="E98" s="3"/>
+      <c r="F98" s="3"/>
+      <c r="G98" s="3"/>
+      <c r="H98" s="3"/>
+      <c r="I98" s="3"/>
+      <c r="J98" s="3"/>
+      <c r="K98" s="3"/>
+      <c r="L98" s="3"/>
+      <c r="M98" s="3"/>
+      <c r="N98" s="3"/>
+      <c r="O98" s="3"/>
+    </row>
+    <row r="99" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A99" s="3"/>
+      <c r="B99" s="3"/>
+      <c r="D99" s="3"/>
+      <c r="E99" s="3"/>
+      <c r="F99" s="3"/>
+      <c r="G99" s="3"/>
+      <c r="H99" s="3"/>
+      <c r="I99" s="3"/>
+      <c r="J99" s="3"/>
+      <c r="K99" s="3"/>
+      <c r="L99" s="3"/>
+      <c r="M99" s="3"/>
+      <c r="N99" s="3"/>
+      <c r="O99" s="3"/>
+    </row>
+    <row r="100" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A100" s="3"/>
+      <c r="B100" s="3"/>
+      <c r="C100" s="3"/>
+      <c r="D100" s="3"/>
+      <c r="E100" s="3"/>
+      <c r="F100" s="3"/>
+      <c r="G100" s="3"/>
+      <c r="H100" s="3"/>
+      <c r="I100" s="3"/>
+      <c r="J100" s="3"/>
+      <c r="K100" s="3"/>
+      <c r="L100" s="3"/>
+      <c r="M100" s="3"/>
+      <c r="N100" s="3"/>
+      <c r="O100" s="3"/>
+    </row>
+    <row r="101" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A101" s="3"/>
+      <c r="B101" s="3"/>
+      <c r="D101" s="3"/>
+      <c r="E101" s="3"/>
+      <c r="F101" s="3"/>
+      <c r="G101" s="3"/>
+      <c r="H101" s="3"/>
+      <c r="I101" s="3"/>
+      <c r="J101" s="3"/>
+      <c r="K101" s="3"/>
+      <c r="L101" s="3"/>
+      <c r="M101" s="3"/>
+      <c r="N101" s="3"/>
+      <c r="O101" s="3"/>
+    </row>
+    <row r="102" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A102" s="3"/>
+      <c r="B102" s="3"/>
+      <c r="C102" s="3"/>
+      <c r="D102" s="3"/>
+      <c r="E102" s="3"/>
+      <c r="F102" s="3"/>
+      <c r="G102" s="3"/>
+      <c r="H102" s="3"/>
+      <c r="I102" s="3"/>
+      <c r="J102" s="3"/>
+      <c r="K102" s="3"/>
+      <c r="L102" s="3"/>
+      <c r="M102" s="3"/>
+      <c r="N102" s="3"/>
+      <c r="O102" s="3"/>
+    </row>
+    <row r="103" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A103" s="3"/>
+      <c r="B103" s="3"/>
+      <c r="D103" s="3"/>
+      <c r="E103" s="3"/>
+      <c r="F103" s="3"/>
+      <c r="G103" s="3"/>
+      <c r="H103" s="3"/>
+      <c r="I103" s="3"/>
+      <c r="J103" s="3"/>
+      <c r="K103" s="3"/>
+      <c r="L103" s="3"/>
+      <c r="M103" s="3"/>
+      <c r="N103" s="3"/>
+      <c r="O103" s="3"/>
+    </row>
+    <row r="104" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A104" s="3"/>
+      <c r="B104" s="3"/>
+      <c r="C104" s="3"/>
+      <c r="D104" s="3"/>
+      <c r="E104" s="3"/>
+      <c r="F104" s="3"/>
+      <c r="G104" s="3"/>
+      <c r="H104" s="3"/>
+      <c r="I104" s="3"/>
+      <c r="J104" s="3"/>
+      <c r="K104" s="3"/>
+      <c r="L104" s="3"/>
+      <c r="M104" s="3"/>
+      <c r="N104" s="3"/>
+      <c r="O104" s="3"/>
+    </row>
+    <row r="105" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A105" s="3"/>
+      <c r="B105" s="3"/>
+      <c r="C105" s="3"/>
+      <c r="D105" s="3"/>
+      <c r="E105" s="3"/>
+      <c r="F105" s="3"/>
+      <c r="G105" s="3"/>
+      <c r="H105" s="3"/>
+      <c r="I105" s="3"/>
+      <c r="J105" s="3"/>
+      <c r="K105" s="3"/>
+      <c r="L105" s="3"/>
+      <c r="M105" s="3"/>
+      <c r="N105" s="3"/>
+      <c r="O105" s="3"/>
+    </row>
+    <row r="106" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A106" s="3"/>
+      <c r="B106" s="3"/>
+      <c r="D106" s="3"/>
+      <c r="E106" s="3"/>
+      <c r="F106" s="3"/>
+      <c r="G106" s="3"/>
+      <c r="H106" s="3"/>
+      <c r="I106" s="3"/>
+      <c r="J106" s="3"/>
+      <c r="K106" s="3"/>
+      <c r="L106" s="3"/>
+      <c r="M106" s="3"/>
+      <c r="N106" s="3"/>
+      <c r="O106" s="3"/>
+    </row>
+    <row r="107" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A107" s="3"/>
+      <c r="B107" s="3"/>
+      <c r="C107" s="3"/>
+      <c r="D107" s="3"/>
+      <c r="E107" s="3"/>
+      <c r="F107" s="3"/>
+      <c r="G107" s="3"/>
+      <c r="H107" s="3"/>
+      <c r="I107" s="3"/>
+      <c r="J107" s="3"/>
+      <c r="K107" s="3"/>
+      <c r="L107" s="3"/>
+      <c r="M107" s="3"/>
+      <c r="N107" s="3"/>
+      <c r="O107" s="3"/>
+    </row>
+    <row r="108" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A108" s="3"/>
+      <c r="B108" s="3"/>
+      <c r="D108" s="3"/>
+      <c r="E108" s="3"/>
+      <c r="F108" s="3"/>
+      <c r="G108" s="3"/>
+      <c r="H108" s="3"/>
+      <c r="I108" s="3"/>
+      <c r="J108" s="3"/>
+      <c r="K108" s="3"/>
+      <c r="L108" s="3"/>
+      <c r="M108" s="3"/>
+      <c r="N108" s="3"/>
+      <c r="O108" s="3"/>
+    </row>
+    <row r="109" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A109" s="3"/>
+      <c r="B109" s="3"/>
+      <c r="C109" s="3"/>
+      <c r="D109" s="3"/>
+      <c r="E109" s="3"/>
+      <c r="F109" s="3"/>
+      <c r="G109" s="3"/>
+      <c r="H109" s="3"/>
+      <c r="I109" s="3"/>
+      <c r="J109" s="3"/>
+      <c r="K109" s="3"/>
+      <c r="L109" s="3"/>
+      <c r="M109" s="3"/>
+      <c r="N109" s="3"/>
+      <c r="O109" s="3"/>
+    </row>
+    <row r="110" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A110" s="3"/>
+      <c r="B110" s="3"/>
+      <c r="D110" s="3"/>
+      <c r="E110" s="3"/>
+      <c r="F110" s="3"/>
+      <c r="G110" s="3"/>
+      <c r="H110" s="3"/>
+      <c r="I110" s="3"/>
+      <c r="J110" s="3"/>
+      <c r="K110" s="3"/>
+      <c r="L110" s="3"/>
+      <c r="M110" s="3"/>
+      <c r="N110" s="3"/>
+      <c r="O110" s="3"/>
+    </row>
+    <row r="111" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="C111" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -707,4 +4039,2577 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AB098BA-D597-40C0-BF44-35AD6CF0A66B}">
+  <dimension ref="A1:O101"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="30" x14ac:dyDescent="0.3">
+      <c r="A5" s="14" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="28" x14ac:dyDescent="0.3">
+      <c r="A7" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="G7" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="H7" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="I7" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="J7" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="K7" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L7" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="M7" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="N7" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="O7" s="12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="84" x14ac:dyDescent="0.3">
+      <c r="A8" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
+      <c r="K8" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="L8" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="M8" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="N8" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="O8" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" ht="70" x14ac:dyDescent="0.3">
+      <c r="A9" s="3"/>
+      <c r="B9" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="I9" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="J9" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="K9" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="L9" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="M9" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="N9" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="O9" s="13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" ht="126" x14ac:dyDescent="0.3">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="I10" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="J10" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="K10" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="L10" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="M10" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="N10" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="O10" s="13" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" ht="56" x14ac:dyDescent="0.3">
+      <c r="A11" s="3"/>
+      <c r="B11" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="I11" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="J11" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="K11" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="L11" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="M11" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="N11" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="O11" s="13" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" ht="84" x14ac:dyDescent="0.3">
+      <c r="A12" s="3"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="I12" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="J12" s="3"/>
+      <c r="K12" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="L12" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M12" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="N12" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="O12" s="13" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" ht="70" x14ac:dyDescent="0.3">
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="I13" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="J13" s="3"/>
+      <c r="K13" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="L13" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="M13" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="N13" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="O13" s="13" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" ht="70" x14ac:dyDescent="0.3">
+      <c r="A14" s="3"/>
+      <c r="B14" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="I14" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="J14" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="K14" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="L14" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M14" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="N14" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="O14" s="13" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" ht="70" x14ac:dyDescent="0.3">
+      <c r="A15" s="3"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="I15" s="3"/>
+      <c r="J15" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="K15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="L15" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="M15" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="N15" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="O15" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" ht="70" x14ac:dyDescent="0.3">
+      <c r="A16" s="3"/>
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="I16" s="3"/>
+      <c r="J16" s="3"/>
+      <c r="K16" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="L16" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M16" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="N16" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="O16" s="13" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" ht="70" x14ac:dyDescent="0.3">
+      <c r="A17" s="3"/>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="I17" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="J17" s="3"/>
+      <c r="K17" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="L17" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M17" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="N17" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="O17" s="13" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" ht="70" x14ac:dyDescent="0.3">
+      <c r="A18" s="3"/>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="I18" s="3"/>
+      <c r="J18" s="3"/>
+      <c r="K18" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="L18" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M18" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="N18" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="O18" s="13" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" ht="70" x14ac:dyDescent="0.3">
+      <c r="A19" s="3"/>
+      <c r="B19" s="3"/>
+      <c r="C19" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="I19" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="J19" s="3"/>
+      <c r="K19" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="L19" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="M19" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="N19" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="O19" s="13" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" ht="56" x14ac:dyDescent="0.3">
+      <c r="A20" s="3"/>
+      <c r="B20" s="3"/>
+      <c r="C20" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="I20" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="J20" s="3"/>
+      <c r="K20" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="L20" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="M20" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="N20" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="O20" s="13" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" ht="70" x14ac:dyDescent="0.3">
+      <c r="A21" s="3"/>
+      <c r="B21" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="I21" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="J21" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="K21" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="L21" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M21" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="N21" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="O21" s="13" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" ht="70" x14ac:dyDescent="0.3">
+      <c r="A22" s="3"/>
+      <c r="B22" s="3"/>
+      <c r="C22" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="I22" s="3"/>
+      <c r="J22" s="3"/>
+      <c r="K22" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="L22" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="M22" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="N22" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="O22" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" ht="84" x14ac:dyDescent="0.3">
+      <c r="A23" s="3"/>
+      <c r="B23" s="3"/>
+      <c r="C23" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="I23" s="3"/>
+      <c r="J23" s="3"/>
+      <c r="K23" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="L23" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="M23" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="N23" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="O23" s="13" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" ht="70" x14ac:dyDescent="0.3">
+      <c r="A24" s="3"/>
+      <c r="B24" s="3"/>
+      <c r="C24" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+      <c r="H24" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="I24" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="J24" s="3"/>
+      <c r="K24" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="L24" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M24" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="N24" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="O24" s="13" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" ht="98" x14ac:dyDescent="0.3">
+      <c r="A25" s="3"/>
+      <c r="B25" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+      <c r="H25" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="I25" s="3"/>
+      <c r="J25" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="K25" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="L25" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M25" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="N25" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="O25" s="13" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" ht="56" x14ac:dyDescent="0.3">
+      <c r="A26" s="3"/>
+      <c r="B26" s="3"/>
+      <c r="C26" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+      <c r="H26" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="I26" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="J26" s="3"/>
+      <c r="K26" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="L26" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M26" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="N26" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="O26" s="13" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" ht="84" x14ac:dyDescent="0.3">
+      <c r="A27" s="3"/>
+      <c r="B27" s="3"/>
+      <c r="C27" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
+      <c r="H27" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="I27" s="3"/>
+      <c r="J27" s="3"/>
+      <c r="K27" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="L27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="M27" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="N27" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="O27" s="13" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" ht="70" x14ac:dyDescent="0.3">
+      <c r="A28" s="3"/>
+      <c r="B28" s="3"/>
+      <c r="C28" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="I28" s="3"/>
+      <c r="J28" s="3"/>
+      <c r="K28" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="L28" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="M28" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="N28" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="O28" s="13" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" ht="70" x14ac:dyDescent="0.3">
+      <c r="A29" s="3"/>
+      <c r="B29" s="3"/>
+      <c r="C29" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
+      <c r="H29" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="I29" s="3"/>
+      <c r="J29" s="3"/>
+      <c r="K29" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="L29" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M29" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="N29" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="O29" s="13" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" ht="84" x14ac:dyDescent="0.3">
+      <c r="A30" s="3"/>
+      <c r="B30" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
+      <c r="H30" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="I30" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="J30" s="3"/>
+      <c r="K30" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="L30" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="M30" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="N30" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="O30" s="13" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" ht="70" x14ac:dyDescent="0.3">
+      <c r="A31" s="3"/>
+      <c r="B31" s="3"/>
+      <c r="C31" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
+      <c r="H31" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="I31" s="3"/>
+      <c r="J31" s="3"/>
+      <c r="K31" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="L31" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M31" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="N31" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="O31" s="13" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" ht="70" x14ac:dyDescent="0.3">
+      <c r="A32" s="3"/>
+      <c r="B32" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3"/>
+      <c r="H32" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="I32" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="J32" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="K32" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="L32" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="M32" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="N32" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="O32" s="13" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" ht="70" x14ac:dyDescent="0.3">
+      <c r="A33" s="3"/>
+      <c r="B33" s="3"/>
+      <c r="C33" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="D33" s="3"/>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3"/>
+      <c r="H33" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="I33" s="3"/>
+      <c r="J33" s="3"/>
+      <c r="K33" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="L33" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="M33" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="N33" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="O33" s="13" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" ht="70" x14ac:dyDescent="0.3">
+      <c r="A34" s="3"/>
+      <c r="B34" s="3"/>
+      <c r="C34" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="D34" s="3"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3"/>
+      <c r="H34" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="I34" s="3"/>
+      <c r="J34" s="3"/>
+      <c r="K34" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="L34" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M34" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="N34" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="O34" s="13" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" ht="84" x14ac:dyDescent="0.3">
+      <c r="A35" s="3"/>
+      <c r="B35" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="C35" s="3"/>
+      <c r="D35" s="3"/>
+      <c r="E35" s="3"/>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3"/>
+      <c r="H35" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="I35" s="3"/>
+      <c r="J35" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="K35" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="L35" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="M35" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="N35" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="O35" s="13" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" ht="56" x14ac:dyDescent="0.3">
+      <c r="A36" s="3"/>
+      <c r="B36" s="3"/>
+      <c r="C36" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="D36" s="3"/>
+      <c r="E36" s="3"/>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3"/>
+      <c r="H36" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="I36" s="3"/>
+      <c r="J36" s="3"/>
+      <c r="K36" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="L36" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="M36" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="N36" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="O36" s="13" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" ht="70" x14ac:dyDescent="0.3">
+      <c r="A37" s="3"/>
+      <c r="B37" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="C37" s="3"/>
+      <c r="D37" s="3"/>
+      <c r="E37" s="3"/>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3"/>
+      <c r="H37" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="I37" s="3"/>
+      <c r="J37" s="3"/>
+      <c r="K37" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="L37" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M37" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="N37" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="O37" s="13" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" ht="42" x14ac:dyDescent="0.3">
+      <c r="A38" s="3"/>
+      <c r="B38" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="C38" s="3"/>
+      <c r="D38" s="3"/>
+      <c r="E38" s="3"/>
+      <c r="F38" s="3"/>
+      <c r="G38" s="3"/>
+      <c r="H38" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="I38" s="3"/>
+      <c r="J38" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="K38" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="L38" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M38" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="N38" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="O38" s="13" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" ht="70" x14ac:dyDescent="0.3">
+      <c r="A39" s="3"/>
+      <c r="B39" s="3"/>
+      <c r="C39" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="D39" s="3"/>
+      <c r="E39" s="3"/>
+      <c r="F39" s="3"/>
+      <c r="G39" s="3"/>
+      <c r="H39" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="I39" s="3"/>
+      <c r="J39" s="3"/>
+      <c r="K39" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="L39" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M39" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="N39" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="O39" s="13" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" ht="98" x14ac:dyDescent="0.3">
+      <c r="A40" s="3"/>
+      <c r="B40" s="3"/>
+      <c r="C40" s="3"/>
+      <c r="D40" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="E40" s="3"/>
+      <c r="F40" s="3"/>
+      <c r="G40" s="3"/>
+      <c r="H40" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="I40" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="J40" s="3"/>
+      <c r="K40" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="L40" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="M40" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="N40" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="O40" s="13" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" ht="70" x14ac:dyDescent="0.3">
+      <c r="A41" s="3"/>
+      <c r="B41" s="3"/>
+      <c r="C41" s="3"/>
+      <c r="D41" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="E41" s="3"/>
+      <c r="F41" s="3"/>
+      <c r="G41" s="3"/>
+      <c r="H41" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="I41" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="J41" s="3"/>
+      <c r="K41" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="L41" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M41" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="N41" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="O41" s="13" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" ht="70" x14ac:dyDescent="0.3">
+      <c r="A42" s="3"/>
+      <c r="B42" s="3"/>
+      <c r="C42" s="3"/>
+      <c r="D42" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="E42" s="3"/>
+      <c r="F42" s="3"/>
+      <c r="G42" s="3"/>
+      <c r="H42" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="I42" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="J42" s="3"/>
+      <c r="K42" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="L42" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M42" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="N42" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="O42" s="13" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" ht="70" x14ac:dyDescent="0.3">
+      <c r="A43" s="3"/>
+      <c r="B43" s="3"/>
+      <c r="C43" s="3"/>
+      <c r="D43" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="E43" s="3"/>
+      <c r="F43" s="3"/>
+      <c r="G43" s="3"/>
+      <c r="H43" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="I43" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="J43" s="3"/>
+      <c r="K43" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="L43" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M43" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="N43" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="O43" s="13" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" ht="70" x14ac:dyDescent="0.3">
+      <c r="A44" s="3"/>
+      <c r="B44" s="3"/>
+      <c r="C44" s="3"/>
+      <c r="D44" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="E44" s="3"/>
+      <c r="F44" s="3"/>
+      <c r="G44" s="3"/>
+      <c r="H44" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="I44" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="J44" s="3"/>
+      <c r="K44" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="L44" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="M44" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="N44" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="O44" s="13" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" ht="70" x14ac:dyDescent="0.3">
+      <c r="A45" s="3"/>
+      <c r="B45" s="3"/>
+      <c r="C45" s="3"/>
+      <c r="D45" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="E45" s="3"/>
+      <c r="F45" s="3"/>
+      <c r="G45" s="3"/>
+      <c r="H45" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="I45" s="3"/>
+      <c r="J45" s="3"/>
+      <c r="K45" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="L45" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M45" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="N45" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="O45" s="13" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" ht="70" x14ac:dyDescent="0.3">
+      <c r="A46" s="3"/>
+      <c r="B46" s="3"/>
+      <c r="C46" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="D46" s="3"/>
+      <c r="E46" s="3"/>
+      <c r="F46" s="3"/>
+      <c r="G46" s="3"/>
+      <c r="H46" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="I46" s="3"/>
+      <c r="J46" s="3"/>
+      <c r="K46" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="L46" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="M46" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="N46" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="O46" s="13" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" ht="70" x14ac:dyDescent="0.3">
+      <c r="A47" s="3"/>
+      <c r="B47" s="3"/>
+      <c r="C47" s="3"/>
+      <c r="D47" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="E47" s="3"/>
+      <c r="F47" s="3"/>
+      <c r="G47" s="3"/>
+      <c r="H47" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="I47" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="J47" s="3"/>
+      <c r="K47" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="L47" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="M47" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="N47" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="O47" s="13" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" ht="70" x14ac:dyDescent="0.3">
+      <c r="A48" s="3"/>
+      <c r="B48" s="3"/>
+      <c r="C48" s="3"/>
+      <c r="D48" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="E48" s="3"/>
+      <c r="F48" s="3"/>
+      <c r="G48" s="3"/>
+      <c r="H48" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="I48" s="13" t="s">
+        <v>166</v>
+      </c>
+      <c r="J48" s="3"/>
+      <c r="K48" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="L48" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="M48" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="N48" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="O48" s="13" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" ht="70" x14ac:dyDescent="0.3">
+      <c r="A49" s="3"/>
+      <c r="B49" s="3"/>
+      <c r="C49" s="3"/>
+      <c r="D49" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="E49" s="3"/>
+      <c r="F49" s="3"/>
+      <c r="G49" s="3"/>
+      <c r="H49" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="I49" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="J49" s="3"/>
+      <c r="K49" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="L49" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="M49" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="N49" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="O49" s="13" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" ht="84" x14ac:dyDescent="0.3">
+      <c r="A50" s="3"/>
+      <c r="B50" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="C50" s="3"/>
+      <c r="D50" s="3"/>
+      <c r="E50" s="3"/>
+      <c r="F50" s="3"/>
+      <c r="G50" s="3"/>
+      <c r="H50" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="I50" s="3"/>
+      <c r="J50" s="3"/>
+      <c r="K50" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="L50" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M50" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="N50" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="O50" s="13" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" ht="56" x14ac:dyDescent="0.3">
+      <c r="A51" s="3"/>
+      <c r="B51" s="3"/>
+      <c r="C51" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="D51" s="3"/>
+      <c r="E51" s="3"/>
+      <c r="F51" s="3"/>
+      <c r="G51" s="3"/>
+      <c r="H51" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="I51" s="3"/>
+      <c r="J51" s="3"/>
+      <c r="K51" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="L51" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="M51" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="N51" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="O51" s="13" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" ht="56" x14ac:dyDescent="0.3">
+      <c r="A52" s="3"/>
+      <c r="B52" s="3"/>
+      <c r="C52" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="D52" s="3"/>
+      <c r="E52" s="3"/>
+      <c r="F52" s="3"/>
+      <c r="G52" s="3"/>
+      <c r="H52" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="I52" s="3"/>
+      <c r="J52" s="3"/>
+      <c r="K52" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="L52" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M52" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="N52" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="O52" s="13" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" ht="56" x14ac:dyDescent="0.3">
+      <c r="A53" s="3"/>
+      <c r="B53" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="C53" s="3"/>
+      <c r="D53" s="3"/>
+      <c r="E53" s="3"/>
+      <c r="F53" s="3"/>
+      <c r="G53" s="3"/>
+      <c r="H53" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="I53" s="3"/>
+      <c r="J53" s="3"/>
+      <c r="K53" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="L53" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="M53" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="N53" s="13" t="s">
+        <v>184</v>
+      </c>
+      <c r="O53" s="13" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" ht="30" x14ac:dyDescent="0.3">
+      <c r="A56" s="14" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A58" s="8" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A59" s="9"/>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A60" s="11" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A61" s="9"/>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A62" s="10" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A63" s="9"/>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A64" s="11" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A65" s="9"/>
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A66" s="11" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A67" s="7"/>
+    </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A68" s="8" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15" ht="30" x14ac:dyDescent="0.3">
+      <c r="A72" s="14" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15" ht="28" x14ac:dyDescent="0.3">
+      <c r="A74" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B74" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C74" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="D74" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="E74" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="F74" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="G74" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="H74" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="I74" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="J74" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="K74" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L74" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="M74" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="N74" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="O74" s="12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15" ht="98" x14ac:dyDescent="0.3">
+      <c r="A75" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="B75" s="3"/>
+      <c r="C75" s="3"/>
+      <c r="D75" s="3"/>
+      <c r="E75" s="3"/>
+      <c r="F75" s="3"/>
+      <c r="G75" s="3"/>
+      <c r="H75" s="13" t="s">
+        <v>194</v>
+      </c>
+      <c r="I75" s="13" t="s">
+        <v>195</v>
+      </c>
+      <c r="J75" s="13" t="s">
+        <v>196</v>
+      </c>
+      <c r="K75" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="L75" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="M75" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="N75" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="O75" s="13" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15" ht="112" x14ac:dyDescent="0.3">
+      <c r="A76" s="3"/>
+      <c r="B76" s="13" t="s">
+        <v>199</v>
+      </c>
+      <c r="C76" s="3"/>
+      <c r="D76" s="3"/>
+      <c r="E76" s="3"/>
+      <c r="F76" s="3"/>
+      <c r="G76" s="3"/>
+      <c r="H76" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="I76" s="13" t="s">
+        <v>200</v>
+      </c>
+      <c r="J76" s="13" t="s">
+        <v>201</v>
+      </c>
+      <c r="K76" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="L76" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="M76" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="N76" s="13" t="s">
+        <v>202</v>
+      </c>
+      <c r="O76" s="13" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15" ht="84" x14ac:dyDescent="0.3">
+      <c r="A77" s="3"/>
+      <c r="B77" s="3"/>
+      <c r="C77" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="D77" s="3"/>
+      <c r="E77" s="3"/>
+      <c r="F77" s="3"/>
+      <c r="G77" s="3"/>
+      <c r="H77" s="13" t="s">
+        <v>199</v>
+      </c>
+      <c r="I77" s="13" t="s">
+        <v>201</v>
+      </c>
+      <c r="J77" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="K77" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="L77" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="M77" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="N77" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="O77" s="13" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15" ht="84" x14ac:dyDescent="0.3">
+      <c r="A78" s="3"/>
+      <c r="B78" s="3"/>
+      <c r="C78" s="13" t="s">
+        <v>207</v>
+      </c>
+      <c r="D78" s="13" t="s">
+        <v>208</v>
+      </c>
+      <c r="E78" s="3"/>
+      <c r="F78" s="3"/>
+      <c r="G78" s="3"/>
+      <c r="H78" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="I78" s="13" t="s">
+        <v>200</v>
+      </c>
+      <c r="J78" s="13" t="s">
+        <v>209</v>
+      </c>
+      <c r="K78" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="L78" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="M78" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="N78" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="O78" s="13" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15" ht="84" x14ac:dyDescent="0.3">
+      <c r="A79" s="3"/>
+      <c r="B79" s="13" t="s">
+        <v>212</v>
+      </c>
+      <c r="C79" s="3"/>
+      <c r="D79" s="3"/>
+      <c r="E79" s="3"/>
+      <c r="F79" s="3"/>
+      <c r="G79" s="3"/>
+      <c r="H79" s="13" t="s">
+        <v>199</v>
+      </c>
+      <c r="I79" s="13" t="s">
+        <v>201</v>
+      </c>
+      <c r="J79" s="13" t="s">
+        <v>213</v>
+      </c>
+      <c r="K79" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="L79" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="M79" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="N79" s="13" t="s">
+        <v>214</v>
+      </c>
+      <c r="O79" s="13" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15" ht="98" x14ac:dyDescent="0.3">
+      <c r="A80" s="3"/>
+      <c r="B80" s="13" t="s">
+        <v>216</v>
+      </c>
+      <c r="C80" s="3"/>
+      <c r="D80" s="3"/>
+      <c r="E80" s="3"/>
+      <c r="F80" s="3"/>
+      <c r="G80" s="3"/>
+      <c r="H80" s="13" t="s">
+        <v>212</v>
+      </c>
+      <c r="I80" s="13" t="s">
+        <v>201</v>
+      </c>
+      <c r="J80" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="K80" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="L80" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="M80" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="N80" s="13" t="s">
+        <v>218</v>
+      </c>
+      <c r="O80" s="13" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="81" spans="1:15" ht="84" x14ac:dyDescent="0.3">
+      <c r="A81" s="3"/>
+      <c r="B81" s="13" t="s">
+        <v>201</v>
+      </c>
+      <c r="C81" s="3"/>
+      <c r="D81" s="3"/>
+      <c r="E81" s="3"/>
+      <c r="F81" s="3"/>
+      <c r="G81" s="3"/>
+      <c r="H81" s="13" t="s">
+        <v>209</v>
+      </c>
+      <c r="I81" s="13" t="s">
+        <v>200</v>
+      </c>
+      <c r="J81" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="K81" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="L81" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="M81" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="N81" s="13" t="s">
+        <v>220</v>
+      </c>
+      <c r="O81" s="13" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="82" spans="1:15" ht="84" x14ac:dyDescent="0.3">
+      <c r="A82" s="3"/>
+      <c r="B82" s="13" t="s">
+        <v>200</v>
+      </c>
+      <c r="C82" s="3"/>
+      <c r="D82" s="3"/>
+      <c r="E82" s="3"/>
+      <c r="F82" s="3"/>
+      <c r="G82" s="3"/>
+      <c r="H82" s="13" t="s">
+        <v>201</v>
+      </c>
+      <c r="I82" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="J82" s="13" t="s">
+        <v>222</v>
+      </c>
+      <c r="K82" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="L82" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M82" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="N82" s="13" t="s">
+        <v>223</v>
+      </c>
+      <c r="O82" s="13" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="83" spans="1:15" ht="56" x14ac:dyDescent="0.3">
+      <c r="A83" s="3"/>
+      <c r="B83" s="3"/>
+      <c r="C83" s="13" t="s">
+        <v>225</v>
+      </c>
+      <c r="D83" s="3"/>
+      <c r="E83" s="3"/>
+      <c r="F83" s="3"/>
+      <c r="G83" s="3"/>
+      <c r="H83" s="13" t="s">
+        <v>200</v>
+      </c>
+      <c r="I83" s="3"/>
+      <c r="J83" s="3"/>
+      <c r="K83" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="L83" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M83" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="N83" s="13" t="s">
+        <v>226</v>
+      </c>
+      <c r="O83" s="13" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="84" spans="1:15" ht="84" x14ac:dyDescent="0.3">
+      <c r="A84" s="3"/>
+      <c r="B84" s="3"/>
+      <c r="C84" s="13" t="s">
+        <v>228</v>
+      </c>
+      <c r="D84" s="3"/>
+      <c r="E84" s="3"/>
+      <c r="F84" s="3"/>
+      <c r="G84" s="3"/>
+      <c r="H84" s="13" t="s">
+        <v>200</v>
+      </c>
+      <c r="I84" s="13" t="s">
+        <v>229</v>
+      </c>
+      <c r="J84" s="13" t="s">
+        <v>230</v>
+      </c>
+      <c r="K84" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="L84" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M84" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="N84" s="13" t="s">
+        <v>231</v>
+      </c>
+      <c r="O84" s="13" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="85" spans="1:15" ht="56" x14ac:dyDescent="0.3">
+      <c r="A85" s="3"/>
+      <c r="B85" s="3"/>
+      <c r="C85" s="13" t="s">
+        <v>229</v>
+      </c>
+      <c r="D85" s="3"/>
+      <c r="E85" s="3"/>
+      <c r="F85" s="3"/>
+      <c r="G85" s="3"/>
+      <c r="H85" s="13" t="s">
+        <v>228</v>
+      </c>
+      <c r="I85" s="13" t="s">
+        <v>233</v>
+      </c>
+      <c r="J85" s="13" t="s">
+        <v>234</v>
+      </c>
+      <c r="K85" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="L85" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M85" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="N85" s="13" t="s">
+        <v>235</v>
+      </c>
+      <c r="O85" s="13" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="86" spans="1:15" ht="56" x14ac:dyDescent="0.3">
+      <c r="A86" s="3"/>
+      <c r="B86" s="3"/>
+      <c r="C86" s="13" t="s">
+        <v>233</v>
+      </c>
+      <c r="D86" s="3"/>
+      <c r="E86" s="3"/>
+      <c r="F86" s="3"/>
+      <c r="G86" s="3"/>
+      <c r="H86" s="13" t="s">
+        <v>229</v>
+      </c>
+      <c r="I86" s="3"/>
+      <c r="J86" s="3"/>
+      <c r="K86" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="L86" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M86" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="N86" s="13" t="s">
+        <v>237</v>
+      </c>
+      <c r="O86" s="13" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="87" spans="1:15" ht="70" x14ac:dyDescent="0.3">
+      <c r="A87" s="3"/>
+      <c r="B87" s="13" t="s">
+        <v>239</v>
+      </c>
+      <c r="C87" s="3"/>
+      <c r="D87" s="3"/>
+      <c r="E87" s="3"/>
+      <c r="F87" s="3"/>
+      <c r="G87" s="3"/>
+      <c r="H87" s="13" t="s">
+        <v>212</v>
+      </c>
+      <c r="I87" s="13" t="s">
+        <v>240</v>
+      </c>
+      <c r="J87" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="K87" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="L87" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="M87" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="N87" s="13" t="s">
+        <v>241</v>
+      </c>
+      <c r="O87" s="13" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="88" spans="1:15" ht="70" x14ac:dyDescent="0.3">
+      <c r="A88" s="3"/>
+      <c r="B88" s="3"/>
+      <c r="C88" s="13" t="s">
+        <v>243</v>
+      </c>
+      <c r="D88" s="3"/>
+      <c r="E88" s="3"/>
+      <c r="F88" s="3"/>
+      <c r="G88" s="3"/>
+      <c r="H88" s="13" t="s">
+        <v>244</v>
+      </c>
+      <c r="I88" s="13" t="s">
+        <v>245</v>
+      </c>
+      <c r="J88" s="13" t="s">
+        <v>246</v>
+      </c>
+      <c r="K88" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="L88" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="M88" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="N88" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="O88" s="13" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="89" spans="1:15" ht="56" x14ac:dyDescent="0.3">
+      <c r="A89" s="3"/>
+      <c r="B89" s="3"/>
+      <c r="C89" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="D89" s="3"/>
+      <c r="E89" s="3"/>
+      <c r="F89" s="3"/>
+      <c r="G89" s="3"/>
+      <c r="H89" s="13" t="s">
+        <v>243</v>
+      </c>
+      <c r="I89" s="13" t="s">
+        <v>246</v>
+      </c>
+      <c r="J89" s="3"/>
+      <c r="K89" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="L89" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M89" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="N89" s="13" t="s">
+        <v>250</v>
+      </c>
+      <c r="O89" s="13" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="90" spans="1:15" ht="84" x14ac:dyDescent="0.3">
+      <c r="A90" s="3"/>
+      <c r="B90" s="3"/>
+      <c r="C90" s="13" t="s">
+        <v>252</v>
+      </c>
+      <c r="D90" s="3"/>
+      <c r="E90" s="3"/>
+      <c r="F90" s="3"/>
+      <c r="G90" s="3"/>
+      <c r="H90" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="I90" s="13" t="s">
+        <v>245</v>
+      </c>
+      <c r="J90" s="13" t="s">
+        <v>253</v>
+      </c>
+      <c r="K90" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="L90" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="M90" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="N90" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="O90" s="13" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="91" spans="1:15" ht="84" x14ac:dyDescent="0.3">
+      <c r="A91" s="3"/>
+      <c r="B91" s="3"/>
+      <c r="C91" s="13" t="s">
+        <v>245</v>
+      </c>
+      <c r="D91" s="3"/>
+      <c r="E91" s="3"/>
+      <c r="F91" s="3"/>
+      <c r="G91" s="3"/>
+      <c r="H91" s="13" t="s">
+        <v>252</v>
+      </c>
+      <c r="I91" s="13" t="s">
+        <v>256</v>
+      </c>
+      <c r="J91" s="3"/>
+      <c r="K91" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="L91" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="M91" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="N91" s="13" t="s">
+        <v>257</v>
+      </c>
+      <c r="O91" s="13" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="92" spans="1:15" ht="70" x14ac:dyDescent="0.3">
+      <c r="A92" s="3"/>
+      <c r="B92" s="3"/>
+      <c r="C92" s="3"/>
+      <c r="D92" s="13" t="s">
+        <v>259</v>
+      </c>
+      <c r="E92" s="3"/>
+      <c r="F92" s="3"/>
+      <c r="G92" s="3"/>
+      <c r="H92" s="13" t="s">
+        <v>245</v>
+      </c>
+      <c r="I92" s="13" t="s">
+        <v>260</v>
+      </c>
+      <c r="J92" s="3"/>
+      <c r="K92" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="L92" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="M92" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="N92" s="13" t="s">
+        <v>261</v>
+      </c>
+      <c r="O92" s="13" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="93" spans="1:15" ht="70" x14ac:dyDescent="0.3">
+      <c r="A93" s="3"/>
+      <c r="B93" s="3"/>
+      <c r="C93" s="3"/>
+      <c r="D93" s="13" t="s">
+        <v>260</v>
+      </c>
+      <c r="E93" s="3"/>
+      <c r="F93" s="3"/>
+      <c r="G93" s="3"/>
+      <c r="H93" s="13" t="s">
+        <v>245</v>
+      </c>
+      <c r="I93" s="13" t="s">
+        <v>263</v>
+      </c>
+      <c r="J93" s="3"/>
+      <c r="K93" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="L93" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="M93" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="N93" s="13" t="s">
+        <v>261</v>
+      </c>
+      <c r="O93" s="13" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="94" spans="1:15" ht="70" x14ac:dyDescent="0.3">
+      <c r="A94" s="3"/>
+      <c r="B94" s="3"/>
+      <c r="C94" s="3"/>
+      <c r="D94" s="13" t="s">
+        <v>263</v>
+      </c>
+      <c r="E94" s="3"/>
+      <c r="F94" s="3"/>
+      <c r="G94" s="3"/>
+      <c r="H94" s="13" t="s">
+        <v>245</v>
+      </c>
+      <c r="I94" s="3"/>
+      <c r="J94" s="3"/>
+      <c r="K94" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="L94" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="M94" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="N94" s="13" t="s">
+        <v>261</v>
+      </c>
+      <c r="O94" s="13" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="95" spans="1:15" ht="98" x14ac:dyDescent="0.3">
+      <c r="A95" s="3"/>
+      <c r="B95" s="13" t="s">
+        <v>266</v>
+      </c>
+      <c r="C95" s="3"/>
+      <c r="D95" s="3"/>
+      <c r="E95" s="3"/>
+      <c r="F95" s="3"/>
+      <c r="G95" s="3"/>
+      <c r="H95" s="13" t="s">
+        <v>244</v>
+      </c>
+      <c r="I95" s="13" t="s">
+        <v>267</v>
+      </c>
+      <c r="J95" s="13" t="s">
+        <v>268</v>
+      </c>
+      <c r="K95" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="L95" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="M95" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="N95" s="13" t="s">
+        <v>269</v>
+      </c>
+      <c r="O95" s="13" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="96" spans="1:15" ht="56" x14ac:dyDescent="0.3">
+      <c r="A96" s="3"/>
+      <c r="B96" s="3"/>
+      <c r="C96" s="13" t="s">
+        <v>271</v>
+      </c>
+      <c r="D96" s="3"/>
+      <c r="E96" s="3"/>
+      <c r="F96" s="3"/>
+      <c r="G96" s="3"/>
+      <c r="H96" s="13" t="s">
+        <v>253</v>
+      </c>
+      <c r="I96" s="13" t="s">
+        <v>267</v>
+      </c>
+      <c r="J96" s="3"/>
+      <c r="K96" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="L96" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="M96" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="N96" s="13" t="s">
+        <v>272</v>
+      </c>
+      <c r="O96" s="13" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="97" spans="1:15" ht="70" x14ac:dyDescent="0.3">
+      <c r="A97" s="3"/>
+      <c r="B97" s="3"/>
+      <c r="C97" s="13" t="s">
+        <v>267</v>
+      </c>
+      <c r="D97" s="3"/>
+      <c r="E97" s="3"/>
+      <c r="F97" s="3"/>
+      <c r="G97" s="3"/>
+      <c r="H97" s="13" t="s">
+        <v>271</v>
+      </c>
+      <c r="I97" s="13" t="s">
+        <v>268</v>
+      </c>
+      <c r="J97" s="3"/>
+      <c r="K97" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="L97" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="M97" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="N97" s="13" t="s">
+        <v>274</v>
+      </c>
+      <c r="O97" s="13" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="98" spans="1:15" ht="84" x14ac:dyDescent="0.3">
+      <c r="A98" s="3"/>
+      <c r="B98" s="3"/>
+      <c r="C98" s="13" t="s">
+        <v>268</v>
+      </c>
+      <c r="D98" s="3"/>
+      <c r="E98" s="3"/>
+      <c r="F98" s="3"/>
+      <c r="G98" s="3"/>
+      <c r="H98" s="13" t="s">
+        <v>267</v>
+      </c>
+      <c r="I98" s="3"/>
+      <c r="J98" s="3"/>
+      <c r="K98" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="L98" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M98" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="N98" s="13" t="s">
+        <v>276</v>
+      </c>
+      <c r="O98" s="13" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="99" spans="1:15" ht="98" x14ac:dyDescent="0.3">
+      <c r="A99" s="3"/>
+      <c r="B99" s="13" t="s">
+        <v>278</v>
+      </c>
+      <c r="C99" s="3"/>
+      <c r="D99" s="3"/>
+      <c r="E99" s="3"/>
+      <c r="F99" s="3"/>
+      <c r="G99" s="3"/>
+      <c r="H99" s="13" t="s">
+        <v>279</v>
+      </c>
+      <c r="I99" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="J99" s="13" t="s">
+        <v>280</v>
+      </c>
+      <c r="K99" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="L99" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M99" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="N99" s="13" t="s">
+        <v>281</v>
+      </c>
+      <c r="O99" s="13" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="100" spans="1:15" ht="70" x14ac:dyDescent="0.3">
+      <c r="A100" s="3"/>
+      <c r="B100" s="3"/>
+      <c r="C100" s="13" t="s">
+        <v>283</v>
+      </c>
+      <c r="D100" s="3"/>
+      <c r="E100" s="3"/>
+      <c r="F100" s="3"/>
+      <c r="G100" s="3"/>
+      <c r="H100" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="I100" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="J100" s="3"/>
+      <c r="K100" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="L100" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="M100" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="N100" s="13" t="s">
+        <v>285</v>
+      </c>
+      <c r="O100" s="13" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="101" spans="1:15" ht="56" x14ac:dyDescent="0.3">
+      <c r="A101" s="3"/>
+      <c r="B101" s="3"/>
+      <c r="C101" s="13" t="s">
+        <v>287</v>
+      </c>
+      <c r="D101" s="3"/>
+      <c r="E101" s="3"/>
+      <c r="F101" s="3"/>
+      <c r="G101" s="3"/>
+      <c r="H101" s="13" t="s">
+        <v>283</v>
+      </c>
+      <c r="I101" s="13" t="s">
+        <v>288</v>
+      </c>
+      <c r="J101" s="3"/>
+      <c r="K101" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="L101" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="M101" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="N101" s="13" t="s">
+        <v>289</v>
+      </c>
+      <c r="O101" s="13" t="s">
+        <v>290</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>